--- a/Deliverable/Main_Board/BOM/(5 Board)Digikey_Main_Board-BOM.xlsx
+++ b/Deliverable/Main_Board/BOM/(5 Board)Digikey_Main_Board-BOM.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2765B983-D2BB-4864-8737-D3AAFD561A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DCEE96-A114-4258-9E60-ECE5F26B1036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="311">
   <si>
     <t>Bill of Material (BOM) for Grant</t>
   </si>
@@ -129,9 +129,6 @@
 </t>
   </si>
   <si>
-    <t>C6, C10, C11, C12, C13, C14, C15, C18, C21, C22, C24, C25, C27, C29, C30, CF2</t>
-  </si>
-  <si>
     <t>Cap 0402</t>
   </si>
   <si>
@@ -380,9 +377,6 @@
     <t>Red 625nm 0402 Light Emitting Diodes (LED) RoHS</t>
   </si>
   <si>
-    <t>LED1, LED2</t>
-  </si>
-  <si>
     <t>LED 0402</t>
   </si>
   <si>
@@ -415,15 +409,6 @@
     <t>UMW</t>
   </si>
   <si>
-    <t>MOSFET P-CH 20V 2.8A SOT-23</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>PMV65XP,215</t>
-  </si>
-  <si>
     <t>MOSFET N-CH 100V .1A SOT23-3</t>
   </si>
   <si>
@@ -445,33 +430,6 @@
     <t>FDN335N</t>
   </si>
   <si>
-    <t>MOSFET N/P-CH 60V/50V SC70-6</t>
-  </si>
-  <si>
-    <t>Q5</t>
-  </si>
-  <si>
-    <t>SOT-363</t>
-  </si>
-  <si>
-    <t>BSS8402DW-7-F</t>
-  </si>
-  <si>
-    <t>Diodes</t>
-  </si>
-  <si>
-    <t>TRANS PNP 60V 3A SOT223</t>
-  </si>
-  <si>
-    <t>QF1</t>
-  </si>
-  <si>
-    <t>NZT660A</t>
-  </si>
-  <si>
-    <t>ON Semiconductor / Fairchild</t>
-  </si>
-  <si>
     <t>Switch</t>
   </si>
   <si>
@@ -485,9 +443,6 @@
   </si>
   <si>
     <t>XKB Enterprise</t>
-  </si>
-  <si>
-    <t>MS12ASG30</t>
   </si>
   <si>
     <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
@@ -581,37 +536,10 @@
     <t>RES SMD 20K OHM 5% 1/16W 0402</t>
   </si>
   <si>
-    <t>R3, R4, R9, R10, R20, RP2</t>
-  </si>
-  <si>
     <t>RC0402JR-0720KL</t>
   </si>
   <si>
     <t>20K</t>
-  </si>
-  <si>
-    <t>RES SMD 2K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>RC0402FR-072KL</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>RES SMD 30.9K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>AC0402FR-0730K9L</t>
-  </si>
-  <si>
-    <t>30.9K</t>
   </si>
   <si>
     <t>RES 10K OHM 5% 1/10W 0402</t>
@@ -690,9 +618,6 @@
     <t>RES SMD 1K OHM 5% 1/10W 0402</t>
   </si>
   <si>
-    <t>R26, RF2</t>
-  </si>
-  <si>
     <t>ERJ-2GEJ102X</t>
   </si>
   <si>
@@ -733,43 +658,6 @@
     <t>4.7K</t>
   </si>
   <si>
-    <t xml:space="preserve">RES 0.068 OHM 1% 1/4W 0805
-</t>
-  </si>
-  <si>
-    <t>RF1</t>
-  </si>
-  <si>
-    <t>RES 0805</t>
-  </si>
-  <si>
-    <t>0805W4F680MT5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(Uniroyal Elec)</t>
-  </si>
-  <si>
-    <t>KDV08FR068ET</t>
-  </si>
-  <si>
-    <t>0.068R</t>
-  </si>
-  <si>
-    <t>RES SMD 1M OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RF3, RF4</t>
-  </si>
-  <si>
-    <t>RC0402FR-071ML</t>
-  </si>
-  <si>
-    <t>RMCF0402JT1M00</t>
-  </si>
-  <si>
-    <t>1M</t>
-  </si>
-  <si>
     <t>RES SMD 118K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -794,21 +682,6 @@
     <t>13.3K</t>
   </si>
   <si>
-    <t>RES 10.5K 0.1W ± 100ppm/℃ 0603</t>
-  </si>
-  <si>
-    <t>RP1</t>
-  </si>
-  <si>
-    <t>RC0603FR-0710K5L</t>
-  </si>
-  <si>
-    <t>CRCW060310K5FKEAC</t>
-  </si>
-  <si>
-    <t>10.5K</t>
-  </si>
-  <si>
     <t>IC</t>
   </si>
   <si>
@@ -825,48 +698,12 @@
   </si>
   <si>
     <t>Exar</t>
-  </si>
-  <si>
-    <t>TVS DIODE 5V 6.8V 6UDFN</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>6UDFN</t>
-  </si>
-  <si>
-    <t>SP3014-02UTG</t>
-  </si>
-  <si>
-    <t>Littelfuse</t>
-  </si>
-  <si>
-    <t>IC VREF SHUNT 18V 0.5% SOT23</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>TLV431BFTA</t>
-  </si>
-  <si>
-    <t>IC COMPARATOR LP DUAL 8-SOIC</t>
-  </si>
-  <si>
-    <t>U4</t>
   </si>
   <si>
     <t xml:space="preserve">8-SOIC
 </t>
   </si>
   <si>
-    <t>LM393DT</t>
-  </si>
-  <si>
-    <t>STMicroelectronics</t>
-  </si>
-  <si>
     <t>IC MCU 32BIT 256KB FLASH 48TQFP</t>
   </si>
   <si>
@@ -916,15 +753,6 @@
   </si>
   <si>
     <t>MCP7940N-I/SN</t>
-  </si>
-  <si>
-    <t>IC LI-ION LDO CHARGE MGMT 8SOIC</t>
-  </si>
-  <si>
-    <t>UF1</t>
-  </si>
-  <si>
-    <t>BQ2057WSNTR</t>
   </si>
   <si>
     <t>IC REG BOOST ADJ 2A SOT23-5</t>
@@ -961,19 +789,6 @@
     <t>PPTC051LFBN-RC</t>
   </si>
   <si>
-    <t>DC Power Receptacle Jack 2.5A 2.5mm 6.5mm SMD Power Connectors RoHS</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
-    <t>DC-005-5A-2.5-SMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCJ250-05-A-K1-A
-</t>
-  </si>
-  <si>
     <t>USB - Micro B Female USB 2 5 SMD USB Connectors RoHS</t>
   </si>
   <si>
@@ -1142,6 +957,24 @@
   </si>
   <si>
     <t xml:space="preserve">Connector </t>
+  </si>
+  <si>
+    <t>C11, C12, C13, C14, C15, C18, C21, C22, C24, C25, C27, C29, C30, CF2</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>R3, R4, R9, R10, R20</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t> LJC18A3-B-Z/BX</t>
+  </si>
+  <si>
+    <t>IP65 rating</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1743,19 +1576,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -1798,7 +1618,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1979,21 +1799,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2024,7 +1835,7 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2039,17 +1850,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2057,7 +1859,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2085,7 +1887,7 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2127,10 +1929,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2140,7 +1939,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2165,6 +1964,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2443,13 +2248,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.85546875" customWidth="1"/>
     <col min="7" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
@@ -2459,27 +2264,27 @@
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="116" t="s">
+      <c r="A1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
-      <c r="E1" s="117"/>
-      <c r="F1" s="117"/>
-      <c r="G1" s="117"/>
-      <c r="H1" s="117"/>
-      <c r="I1" s="117"/>
-      <c r="J1" s="117"/>
-      <c r="K1" s="117"/>
-      <c r="L1" s="117"/>
-      <c r="M1" s="117"/>
-      <c r="N1" s="117"/>
-      <c r="O1" s="118"/>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="111"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
@@ -2532,7 +2337,7 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="121" t="s">
+      <c r="B3" s="114" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="13" t="s">
@@ -2560,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="15">
-        <f t="shared" ref="K3:K66" si="0">J3*5</f>
+        <f t="shared" ref="K3:K53" si="0">J3*5</f>
         <v>5</v>
       </c>
       <c r="L3" s="16" t="s">
@@ -2570,7 +2375,7 @@
         <v>0.43</v>
       </c>
       <c r="N3" s="18">
-        <f t="shared" ref="N3:N65" si="1">M3*K3</f>
+        <f t="shared" ref="N3:N52" si="1">M3*K3</f>
         <v>2.15</v>
       </c>
       <c r="O3" s="19"/>
@@ -2579,7 +2384,7 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="122"/>
+      <c r="B4" s="115"/>
       <c r="C4" s="20" t="s">
         <v>25</v>
       </c>
@@ -2624,34 +2429,34 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="122"/>
+      <c r="B5" s="115"/>
       <c r="C5" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="112" t="s">
+      <c r="D5" s="106" t="s">
+        <v>305</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="G5" s="23" t="s">
         <v>34</v>
-      </c>
-      <c r="G5" s="23" t="s">
-        <v>35</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" s="23">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5" s="23">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L5" s="28" t="s">
         <v>24</v>
@@ -2661,7 +2466,7 @@
       </c>
       <c r="N5" s="26">
         <f t="shared" si="1"/>
-        <v>1.2640000000000002</v>
+        <v>1.1060000000000001</v>
       </c>
       <c r="O5" s="27"/>
     </row>
@@ -2669,27 +2474,27 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="122"/>
+      <c r="B6" s="115"/>
       <c r="C6" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="E6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="F6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="23" t="s">
         <v>40</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>41</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6" s="23">
         <v>2</v>
@@ -2714,27 +2519,27 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="122"/>
+      <c r="B7" s="115"/>
       <c r="C7" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>43</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>44</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>19</v>
       </c>
       <c r="F7" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="23" t="s">
         <v>45</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>46</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7" s="23">
         <v>2</v>
@@ -2759,27 +2564,27 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="122"/>
+      <c r="B8" s="115"/>
       <c r="C8" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="E8" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="F8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="G8" s="23" t="s">
         <v>51</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>52</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J8" s="23">
         <v>1</v>
@@ -2804,27 +2609,27 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="122"/>
+      <c r="B9" s="115"/>
       <c r="C9" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="E9" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="F9" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="G9" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="21" t="s">
+      <c r="I9" s="21" t="s">
         <v>58</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>59</v>
       </c>
       <c r="J9" s="23">
         <v>4</v>
@@ -2849,27 +2654,27 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="122"/>
+      <c r="B10" s="115"/>
       <c r="C10" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="21" t="s">
+      <c r="G10" s="23" t="s">
         <v>62</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>63</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J10" s="23">
         <v>1</v>
@@ -2894,27 +2699,27 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="122"/>
+      <c r="B11" s="115"/>
       <c r="C11" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="G11" s="23" t="s">
         <v>68</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>69</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J11" s="23">
         <v>1</v>
@@ -2924,7 +2729,7 @@
         <v>5</v>
       </c>
       <c r="L11" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M11" s="26">
         <v>0.44</v>
@@ -2939,27 +2744,27 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="122"/>
+      <c r="B12" s="115"/>
       <c r="C12" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="21" t="s">
         <v>72</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>73</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="23" t="s">
         <v>74</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>75</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J12" s="23">
         <v>1</v>
@@ -2969,7 +2774,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M12" s="33">
         <v>0.6411</v>
@@ -2984,27 +2789,27 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="122"/>
+      <c r="B13" s="115"/>
       <c r="C13" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="E13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="21" t="s">
+      <c r="G13" s="23" t="s">
         <v>80</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>81</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J13" s="23">
         <v>1</v>
@@ -3029,27 +2834,27 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="122"/>
+      <c r="B14" s="115"/>
       <c r="C14" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="E14" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="21" t="s">
+      <c r="G14" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="G14" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J14" s="23">
         <v>1</v>
@@ -3074,27 +2879,27 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="122"/>
+      <c r="B15" s="115"/>
       <c r="C15" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="21" t="s">
+      <c r="G15" s="23" t="s">
         <v>90</v>
-      </c>
-      <c r="G15" s="23" t="s">
-        <v>91</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J15" s="36">
         <v>1</v>
@@ -3119,27 +2924,27 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="122"/>
+      <c r="B16" s="115"/>
       <c r="C16" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="E16" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="39" t="s">
+      <c r="G16" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="H16" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="I16" s="39" t="s">
         <v>97</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>98</v>
       </c>
       <c r="J16" s="34">
         <v>1</v>
@@ -3164,26 +2969,26 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="121" t="s">
+      <c r="B17" s="114" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="D17" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="E17" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="F17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="G17" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>104</v>
-      </c>
       <c r="H17" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I17" s="14" t="s">
         <v>22</v>
@@ -3195,8 +3000,8 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L17" s="113" t="s">
-        <v>105</v>
+      <c r="L17" s="107" t="s">
+        <v>104</v>
       </c>
       <c r="M17" s="46">
         <v>0.5</v>
@@ -3211,27 +3016,27 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="123"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="E18" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="F18" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="G18" s="51" t="s">
         <v>109</v>
       </c>
-      <c r="G18" s="51" t="s">
+      <c r="H18" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="H18" s="50" t="s">
+      <c r="I18" s="50" t="s">
         <v>111</v>
-      </c>
-      <c r="I18" s="50" t="s">
-        <v>112</v>
       </c>
       <c r="J18" s="51">
         <v>2</v>
@@ -3241,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="L18" s="52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M18" s="53">
         <v>0.32200000000000001</v>
@@ -3257,35 +3062,35 @@
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C19" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="D19" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="E19" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="56" t="s">
+      <c r="F19" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="G19" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="F19" s="57" t="s">
+      <c r="H19" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="G19" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="H19" s="56" t="s">
-        <v>119</v>
-      </c>
       <c r="I19" s="56" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J19" s="40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" s="40">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L19" s="58" t="s">
         <v>24</v>
@@ -3295,7 +3100,7 @@
       </c>
       <c r="N19" s="59">
         <f t="shared" si="1"/>
-        <v>3.22</v>
+        <v>1.61</v>
       </c>
       <c r="O19" s="60"/>
     </row>
@@ -3303,29 +3108,29 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="121" t="s">
+      <c r="B20" s="114" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="F20" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="G20" s="15" t="s">
         <v>123</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>125</v>
       </c>
       <c r="H20" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" s="15">
         <v>1</v>
@@ -3348,29 +3153,29 @@
     </row>
     <row r="21" spans="1:15" ht="15.75" thickBot="1">
       <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="122"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="115"/>
       <c r="C21" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="G21" s="23" t="s">
         <v>127</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="G21" s="23" t="s">
-        <v>110</v>
       </c>
       <c r="H21" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J21" s="23">
         <v>1</v>
@@ -3383,39 +3188,39 @@
         <v>24</v>
       </c>
       <c r="M21" s="26">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="N21" s="26">
         <f t="shared" si="1"/>
-        <v>2.3499999999999996</v>
+        <v>3.35</v>
       </c>
       <c r="O21" s="31"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1">
       <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="122"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="115"/>
       <c r="C22" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="E22" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="G22" s="23" t="s">
         <v>123</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>132</v>
       </c>
       <c r="H22" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I22" s="62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J22" s="23">
         <v>1</v>
@@ -3424,387 +3229,391 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L22" s="24" t="s">
+      <c r="L22" s="29" t="s">
         <v>24</v>
       </c>
       <c r="M22" s="26">
-        <v>0.67</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="N22" s="26">
         <f t="shared" si="1"/>
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="O22" s="31"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1">
       <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="122"/>
-      <c r="C23" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="115" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="62" t="s">
         <v>133</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="E23" s="62" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="121" t="s">
         <v>134</v>
       </c>
-      <c r="E23" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="21" t="s">
+      <c r="G23" s="66" t="s">
         <v>135</v>
-      </c>
-      <c r="G23" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="J23" s="23">
+        <v>111</v>
+      </c>
+      <c r="J23" s="66">
         <v>1</v>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="66">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L23" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="26">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N23" s="26">
+      <c r="L23" s="67" t="s">
+        <v>290</v>
+      </c>
+      <c r="M23" s="68">
+        <v>1.5</v>
+      </c>
+      <c r="N23" s="68">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="O23" s="31"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1">
       <c r="A24" s="1">
+        <v>25</v>
+      </c>
+      <c r="B24" s="115"/>
+      <c r="C24" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="122"/>
-      <c r="C24" s="63" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="H24" s="23"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="23">
+      <c r="I24" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J24" s="34">
         <v>1</v>
       </c>
-      <c r="K24" s="23">
+      <c r="K24" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L24" s="72" t="s">
+      <c r="L24" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="65">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N24" s="26">
+      <c r="M24" s="37">
+        <v>1.01</v>
+      </c>
+      <c r="N24" s="37">
         <f t="shared" si="1"/>
-        <v>2.75</v>
+        <v>5.05</v>
       </c>
       <c r="O24" s="43"/>
     </row>
-    <row r="25" spans="1:15" ht="15.75" thickBot="1">
+    <row r="25" spans="1:15" ht="16.5" thickBot="1">
       <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="123"/>
-      <c r="C25" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="71" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="50" t="s">
+      <c r="E25" s="71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="G25" s="51" t="s">
+      <c r="G25" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="H25" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="J25" s="51">
+      <c r="H25" s="73" t="s">
+        <v>145</v>
+      </c>
+      <c r="I25" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="J25" s="73">
         <v>1</v>
       </c>
-      <c r="K25" s="51">
+      <c r="K25" s="73">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L25" s="52" t="s">
+      <c r="L25" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="M25" s="53">
-        <v>0.64</v>
-      </c>
-      <c r="N25" s="53">
+      <c r="M25" s="75">
+        <v>0.68</v>
+      </c>
+      <c r="N25" s="75">
         <f t="shared" si="1"/>
-        <v>3.2</v>
-      </c>
-      <c r="O25" s="54"/>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1">
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="O25" s="76"/>
+    </row>
+    <row r="26" spans="1:15" ht="16.5" thickBot="1">
       <c r="A26" s="1">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E26" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="56" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="H26" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="J26" s="40">
+        <v>2</v>
+      </c>
+      <c r="K26" s="40">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L26" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="122" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="68" t="s">
-        <v>148</v>
-      </c>
-      <c r="G26" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="H26" s="62" t="s">
-        <v>150</v>
-      </c>
-      <c r="I26" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="J26" s="69">
+      <c r="M26" s="59">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="N26" s="59">
+        <f t="shared" si="1"/>
+        <v>6.54</v>
+      </c>
+      <c r="O26" s="60"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A27" s="1">
+        <v>28</v>
+      </c>
+      <c r="B27" s="114" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" s="78" t="s">
+        <v>155</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="J27" s="15">
         <v>1</v>
       </c>
-      <c r="K26" s="69">
+      <c r="K27" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L26" s="70" t="s">
+      <c r="L27" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="71">
-        <v>6.32</v>
-      </c>
-      <c r="N26" s="71">
+      <c r="M27" s="47">
+        <v>0.1</v>
+      </c>
+      <c r="N27" s="47">
         <f t="shared" si="1"/>
-        <v>31.6</v>
-      </c>
-      <c r="O26" s="31"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A27" s="1">
-        <v>25</v>
-      </c>
-      <c r="B27" s="122"/>
-      <c r="C27" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="G27" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="H27" s="39" t="s">
+        <v>0.5</v>
+      </c>
+      <c r="O27" s="48"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A28" s="1">
+        <v>29</v>
+      </c>
+      <c r="B28" s="115"/>
+      <c r="C28" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="H28" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="J27" s="34">
+      <c r="I28" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="J28" s="23">
         <v>1</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K28" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="72" t="s">
+      <c r="L28" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M27" s="37">
-        <v>1.01</v>
-      </c>
-      <c r="N27" s="37">
+      <c r="M28" s="26">
+        <v>0.1</v>
+      </c>
+      <c r="N28" s="26">
         <f t="shared" si="1"/>
-        <v>5.05</v>
-      </c>
-      <c r="O27" s="43"/>
-    </row>
-    <row r="28" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C28" s="73" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="74" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="75" t="s">
-        <v>158</v>
-      </c>
-      <c r="G28" s="76" t="s">
-        <v>159</v>
-      </c>
-      <c r="H28" s="76" t="s">
-        <v>160</v>
-      </c>
-      <c r="I28" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="J28" s="76">
-        <v>1</v>
-      </c>
-      <c r="K28" s="76">
+        <v>0.5</v>
+      </c>
+      <c r="O28" s="32"/>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A29" s="1">
+        <v>30</v>
+      </c>
+      <c r="B29" s="115"/>
+      <c r="C29" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="J29" s="23">
+        <v>5</v>
+      </c>
+      <c r="K29" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L28" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="78">
-        <v>0.68</v>
-      </c>
-      <c r="N28" s="78">
+      <c r="M29" s="26">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="N29" s="26">
         <f t="shared" si="1"/>
-        <v>3.4000000000000004</v>
-      </c>
-      <c r="O28" s="79"/>
-    </row>
-    <row r="29" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A29" s="1">
-        <v>27</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C29" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="D29" s="56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E29" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="56" t="s">
-        <v>164</v>
-      </c>
-      <c r="G29" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="H29" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="J29" s="40">
-        <v>2</v>
-      </c>
-      <c r="K29" s="40">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L29" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="59">
-        <v>0.65400000000000003</v>
-      </c>
-      <c r="N29" s="59">
-        <f t="shared" si="1"/>
-        <v>6.54</v>
-      </c>
-      <c r="O29" s="60"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="O29" s="32"/>
     </row>
     <row r="30" spans="1:15" ht="15.75" thickBot="1">
       <c r="A30" s="1">
-        <v>28</v>
-      </c>
-      <c r="B30" s="121" t="s">
-        <v>166</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="115"/>
+      <c r="C30" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="D30" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="F30" s="81" t="s">
+      <c r="E30" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="G30" s="15" t="s">
+      <c r="G30" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H30" s="80" t="s">
         <v>172</v>
       </c>
-      <c r="I30" s="14" t="s">
+      <c r="I30" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="J30" s="15">
-        <v>1</v>
-      </c>
-      <c r="K30" s="15">
+      <c r="J30" s="23">
+        <v>9</v>
+      </c>
+      <c r="K30" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L30" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M30" s="47">
-        <v>0.1</v>
-      </c>
-      <c r="N30" s="47">
+      <c r="M30" s="26">
+        <v>0.223</v>
+      </c>
+      <c r="N30" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O30" s="48"/>
+        <v>10.035</v>
+      </c>
+      <c r="O30" s="31"/>
     </row>
     <row r="31" spans="1:15" ht="15.75" thickBot="1">
       <c r="A31" s="1">
-        <v>29</v>
-      </c>
-      <c r="B31" s="122"/>
+        <v>34</v>
+      </c>
+      <c r="B31" s="115"/>
       <c r="C31" s="20" t="s">
         <v>174</v>
       </c>
@@ -3812,19 +3621,19 @@
         <v>175</v>
       </c>
       <c r="E31" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="F31" s="21" t="s">
-        <v>177</v>
-      </c>
       <c r="G31" s="23" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="H31" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I31" s="21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J31" s="23">
         <v>1</v>
@@ -3834,112 +3643,112 @@
         <v>5</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="M31" s="26">
-        <v>0.1</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="N31" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.505</v>
       </c>
       <c r="O31" s="32"/>
     </row>
     <row r="32" spans="1:15" ht="15.75" thickBot="1">
       <c r="A32" s="1">
-        <v>30</v>
-      </c>
-      <c r="B32" s="122"/>
+        <v>35</v>
+      </c>
+      <c r="B32" s="115"/>
       <c r="C32" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F32" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="G32" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F32" s="21" t="s">
+      <c r="I32" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="G32" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>183</v>
-      </c>
       <c r="J32" s="23">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K32" s="23">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="L32" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M32" s="26">
-        <v>1.2999999999999999E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N32" s="26">
         <f t="shared" si="1"/>
-        <v>0.38999999999999996</v>
-      </c>
-      <c r="O32" s="32"/>
+        <v>0.5</v>
+      </c>
+      <c r="O32" s="31"/>
     </row>
     <row r="33" spans="1:15" ht="15.75" thickBot="1">
       <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" s="122"/>
+        <v>36</v>
+      </c>
+      <c r="B33" s="115"/>
       <c r="C33" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="E33" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="E33" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="21" t="s">
+      <c r="G33" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="23" t="s">
         <v>186</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>22</v>
       </c>
       <c r="I33" s="21" t="s">
         <v>187</v>
       </c>
       <c r="J33" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K33" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L33" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M33" s="26">
-        <v>0.1</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="N33" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O33" s="32"/>
+        <v>0.26</v>
+      </c>
+      <c r="O33" s="31"/>
     </row>
     <row r="34" spans="1:15" ht="15.75" thickBot="1">
       <c r="A34" s="1">
-        <v>32</v>
-      </c>
-      <c r="B34" s="122"/>
+        <v>37</v>
+      </c>
+      <c r="B34" s="115"/>
       <c r="C34" s="20" t="s">
         <v>188</v>
       </c>
@@ -3947,13 +3756,13 @@
         <v>189</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>190</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H34" s="21" t="s">
         <v>22</v>
@@ -3962,139 +3771,137 @@
         <v>191</v>
       </c>
       <c r="J34" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L34" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M34" s="26">
-        <v>0.1</v>
+        <v>1.6E-2</v>
       </c>
       <c r="N34" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.24</v>
       </c>
       <c r="O34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="15.75" thickBot="1">
       <c r="A35" s="1">
-        <v>33</v>
-      </c>
-      <c r="B35" s="122"/>
+        <v>38</v>
+      </c>
+      <c r="B35" s="115"/>
       <c r="C35" s="20" t="s">
         <v>192</v>
       </c>
       <c r="D35" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="E35" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F35" s="22" t="s">
+      <c r="G35" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="G35" s="23" t="s">
+      <c r="I35" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="H35" s="83" t="s">
-        <v>196</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>197</v>
-      </c>
       <c r="J35" s="23">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K35" s="23">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="L35" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M35" s="26">
-        <v>0.223</v>
+        <v>0.1</v>
       </c>
       <c r="N35" s="26">
         <f t="shared" si="1"/>
-        <v>10.035</v>
+        <v>0.5</v>
       </c>
       <c r="O35" s="31"/>
     </row>
     <row r="36" spans="1:15" ht="15.75" thickBot="1">
       <c r="A36" s="1">
-        <v>34</v>
-      </c>
-      <c r="B36" s="122"/>
-      <c r="C36" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="115"/>
+      <c r="C36" s="63" t="s">
+        <v>196</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="22" t="s">
         <v>198</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="G36" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F36" s="21" t="s">
+      <c r="I36" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="G36" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>201</v>
-      </c>
       <c r="J36" s="23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K36" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="M36" s="26">
-        <v>0.10100000000000001</v>
+        <v>24</v>
+      </c>
+      <c r="M36" s="64">
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="N36" s="26">
         <f t="shared" si="1"/>
-        <v>0.505</v>
-      </c>
-      <c r="O36" s="32"/>
+        <v>0.26</v>
+      </c>
+      <c r="O36" s="31"/>
     </row>
     <row r="37" spans="1:15" ht="15.75" thickBot="1">
       <c r="A37" s="1">
-        <v>35</v>
-      </c>
-      <c r="B37" s="122"/>
-      <c r="C37" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="115"/>
+      <c r="C37" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="E37" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F37" s="22" t="s">
+      <c r="F37" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="G37" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="H37" s="23" t="s">
+      <c r="G37" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="23"/>
+      <c r="I37" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="I37" s="21" t="s">
-        <v>206</v>
       </c>
       <c r="J37" s="23">
         <v>1</v>
@@ -4106,201 +3913,203 @@
       <c r="L37" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M37" s="26">
+      <c r="M37" s="64">
         <v>0.1</v>
       </c>
       <c r="N37" s="26">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="O37" s="31"/>
+      <c r="O37" s="32"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" thickBot="1">
       <c r="A38" s="1">
-        <v>36</v>
-      </c>
-      <c r="B38" s="122"/>
+        <v>43</v>
+      </c>
+      <c r="B38" s="115"/>
       <c r="C38" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D38" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="E38" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F38" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="E38" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F38" s="22" t="s">
+      <c r="G38" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="G38" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H38" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="I38" s="21" t="s">
-        <v>211</v>
-      </c>
       <c r="J38" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K38" s="23">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L38" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M38" s="26">
-        <v>1.2E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N38" s="26">
         <f t="shared" si="1"/>
-        <v>0.24</v>
-      </c>
-      <c r="O38" s="31"/>
+        <v>0.5</v>
+      </c>
+      <c r="O38" s="32"/>
     </row>
     <row r="39" spans="1:15" ht="15.75" thickBot="1">
       <c r="A39" s="1">
-        <v>37</v>
-      </c>
-      <c r="B39" s="122"/>
+        <v>44</v>
+      </c>
+      <c r="B39" s="115"/>
       <c r="C39" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="D39" s="21" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>214</v>
-      </c>
       <c r="G39" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H39" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J39" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K39" s="23">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L39" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M39" s="26">
-        <v>1.6E-2</v>
+        <v>0.1</v>
       </c>
       <c r="N39" s="26">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="O39" s="32"/>
     </row>
     <row r="40" spans="1:15" ht="15.75" thickBot="1">
       <c r="A40" s="1">
-        <v>38</v>
-      </c>
-      <c r="B40" s="122"/>
-      <c r="C40" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="114" t="s">
+        <v>214</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="E40" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E40" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F40" s="22" t="s">
+      <c r="F40" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="G40" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H40" s="23" t="s">
+      <c r="G40" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="I40" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="J40" s="23">
-        <v>2</v>
-      </c>
-      <c r="K40" s="23">
+      <c r="H40" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="J40" s="15">
+        <v>1</v>
+      </c>
+      <c r="K40" s="15">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L40" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="M40" s="26">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="N40" s="26">
+      <c r="M40" s="47">
+        <v>1.2</v>
+      </c>
+      <c r="N40" s="47">
         <f t="shared" si="1"/>
-        <v>0.13</v>
-      </c>
-      <c r="O40" s="31"/>
+        <v>6</v>
+      </c>
+      <c r="O40" s="61"/>
     </row>
     <row r="41" spans="1:15" ht="15.75" thickBot="1">
       <c r="A41" s="1">
-        <v>39</v>
-      </c>
-      <c r="B41" s="122"/>
-      <c r="C41" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="115"/>
+      <c r="C41" s="20" t="s">
         <v>221</v>
       </c>
       <c r="D41" s="21" t="s">
         <v>222</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F41" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="G41" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="23" t="s">
+      <c r="F41" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="I41" s="23" t="s">
+      <c r="G41" s="23" t="s">
         <v>225</v>
       </c>
+      <c r="H41" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="21" t="s">
+        <v>111</v>
+      </c>
       <c r="J41" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K41" s="23">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L41" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M41" s="65">
-        <v>1.2999999999999999E-2</v>
+      <c r="M41" s="26">
+        <v>4.2300000000000004</v>
       </c>
       <c r="N41" s="26">
         <f t="shared" si="1"/>
-        <v>0.26</v>
+        <v>21.150000000000002</v>
       </c>
       <c r="O41" s="31"/>
     </row>
     <row r="42" spans="1:15" ht="15.75" thickBot="1">
       <c r="A42" s="1">
-        <v>40</v>
-      </c>
-      <c r="B42" s="122"/>
-      <c r="C42" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="115"/>
+      <c r="C42" s="20" t="s">
         <v>226</v>
       </c>
       <c r="D42" s="21" t="s">
@@ -4312,12 +4121,14 @@
       <c r="F42" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="G42" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23" t="s">
+      <c r="G42" s="23" t="s">
         <v>230</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="21" t="s">
+        <v>111</v>
       </c>
       <c r="J42" s="23">
         <v>1</v>
@@ -4327,22 +4138,22 @@
         <v>5</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M42" s="65">
-        <v>0.1</v>
+        <v>76</v>
+      </c>
+      <c r="M42" s="26">
+        <v>1.3006</v>
       </c>
       <c r="N42" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>6.5030000000000001</v>
       </c>
       <c r="O42" s="32"/>
     </row>
     <row r="43" spans="1:15" ht="15.75" thickBot="1">
       <c r="A43" s="1">
-        <v>41</v>
-      </c>
-      <c r="B43" s="122"/>
+        <v>52</v>
+      </c>
+      <c r="B43" s="115"/>
       <c r="C43" s="20" t="s">
         <v>231</v>
       </c>
@@ -4352,17 +4163,17 @@
       <c r="E43" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="21" t="s">
         <v>234</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="H43" s="23" t="s">
-        <v>236</v>
+        <v>230</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>22</v>
       </c>
       <c r="I43" s="21" t="s">
-        <v>237</v>
+        <v>111</v>
       </c>
       <c r="J43" s="23">
         <v>1</v>
@@ -4375,129 +4186,131 @@
         <v>24</v>
       </c>
       <c r="M43" s="26">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="N43" s="26">
         <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-      <c r="O43" s="32"/>
+        <v>12</v>
+      </c>
+      <c r="O43" s="31"/>
     </row>
     <row r="44" spans="1:15" ht="15.75" thickBot="1">
       <c r="A44" s="1">
-        <v>42</v>
-      </c>
-      <c r="B44" s="122"/>
+        <v>53</v>
+      </c>
+      <c r="B44" s="115"/>
       <c r="C44" s="20" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>240</v>
+        <v>220</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>237</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>241</v>
+        <v>225</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>22</v>
       </c>
       <c r="I44" s="21" t="s">
-        <v>242</v>
+        <v>111</v>
       </c>
       <c r="J44" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K44" s="23">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L44" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M44" s="26">
-        <v>1.2E-2</v>
+        <v>0.86</v>
       </c>
       <c r="N44" s="26">
         <f t="shared" si="1"/>
-        <v>0.12</v>
+        <v>4.3</v>
       </c>
       <c r="O44" s="31"/>
     </row>
     <row r="45" spans="1:15" ht="15.75" thickBot="1">
       <c r="A45" s="1">
-        <v>43</v>
-      </c>
-      <c r="B45" s="122"/>
-      <c r="C45" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="116"/>
+      <c r="C45" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="F45" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="G45" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="H45" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="G45" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H45" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I45" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="J45" s="23">
+      <c r="I45" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="J45" s="51">
         <v>1</v>
       </c>
-      <c r="K45" s="23">
+      <c r="K45" s="51">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L45" s="24" t="s">
+      <c r="L45" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="M45" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="N45" s="26">
+      <c r="M45" s="53">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N45" s="53">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O45" s="32"/>
+        <v>5.75</v>
+      </c>
+      <c r="O45" s="54"/>
     </row>
     <row r="46" spans="1:15" ht="15.75" thickBot="1">
       <c r="A46" s="1">
-        <v>44</v>
-      </c>
-      <c r="B46" s="122"/>
-      <c r="C46" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="117" t="s">
+        <v>304</v>
+      </c>
+      <c r="C46" s="82" t="s">
+        <v>244</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="G46" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="H46" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="F46" s="21" t="s">
-        <v>249</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="H46" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="21" t="s">
-        <v>250</v>
+      <c r="I46" s="14" t="s">
+        <v>111</v>
       </c>
       <c r="J46" s="23">
         <v>1</v>
@@ -4506,135 +4319,133 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L46" s="24" t="s">
+      <c r="L46" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="M46" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="N46" s="26">
+      <c r="M46" s="64">
+        <v>0.47</v>
+      </c>
+      <c r="N46" s="37">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O46" s="32"/>
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="O46" s="84"/>
     </row>
     <row r="47" spans="1:15" ht="15.75" thickBot="1">
       <c r="A47" s="1">
-        <v>45</v>
-      </c>
-      <c r="B47" s="123"/>
-      <c r="C47" s="84" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" s="115"/>
+      <c r="C47" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="D47" s="50" t="s">
+      <c r="G47" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="E47" s="50" t="s">
-        <v>228</v>
-      </c>
-      <c r="F47" s="85" t="s">
+      <c r="H47" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="G47" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="H47" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="I47" s="114" t="s">
-        <v>255</v>
-      </c>
-      <c r="J47" s="51">
+      <c r="I47" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J47" s="23">
         <v>1</v>
       </c>
-      <c r="K47" s="51">
+      <c r="K47" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L47" s="52" t="s">
+      <c r="L47" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="86">
-        <v>0.1</v>
-      </c>
-      <c r="N47" s="53">
+      <c r="M47" s="26">
+        <v>0.35</v>
+      </c>
+      <c r="N47" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O47" s="87"/>
+        <v>1.75</v>
+      </c>
+      <c r="O47" s="31"/>
     </row>
     <row r="48" spans="1:15" ht="15.75" thickBot="1">
       <c r="A48" s="1">
-        <v>46</v>
-      </c>
-      <c r="B48" s="121" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="115"/>
+      <c r="C48" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="G48" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="D48" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="F48" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="G48" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="H48" s="14" t="s">
+      <c r="H48" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="I48" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="J48" s="15">
+      <c r="I48" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J48" s="23">
         <v>1</v>
       </c>
-      <c r="K48" s="15">
+      <c r="K48" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L48" s="16" t="s">
+      <c r="L48" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="M48" s="47">
-        <v>1.2</v>
-      </c>
-      <c r="N48" s="47">
+      <c r="M48" s="26">
+        <v>0.96</v>
+      </c>
+      <c r="N48" s="26">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="O48" s="61"/>
+        <v>4.8</v>
+      </c>
+      <c r="O48" s="32"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" thickBot="1">
       <c r="A49" s="1">
-        <v>47</v>
-      </c>
-      <c r="B49" s="122"/>
+        <v>60</v>
+      </c>
+      <c r="B49" s="115"/>
       <c r="C49" s="20" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>265</v>
+        <v>19</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>260</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="H49" s="21" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>261</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J49" s="23">
         <v>1</v>
@@ -4644,42 +4455,42 @@
         <v>5</v>
       </c>
       <c r="L49" s="24" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="M49" s="26">
-        <v>0.65400000000000003</v>
+        <v>0.15</v>
       </c>
       <c r="N49" s="26">
         <f t="shared" si="1"/>
-        <v>3.27</v>
-      </c>
-      <c r="O49" s="31"/>
+        <v>0.75</v>
+      </c>
+      <c r="O49" s="32"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" thickBot="1">
       <c r="A50" s="1">
-        <v>48</v>
-      </c>
-      <c r="B50" s="122"/>
+        <v>61</v>
+      </c>
+      <c r="B50" s="115"/>
       <c r="C50" s="20" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>269</v>
+        <v>19</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>264</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>22</v>
+        <v>265</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>266</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J50" s="23">
         <v>1</v>
@@ -4692,39 +4503,39 @@
         <v>24</v>
       </c>
       <c r="M50" s="26">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="N50" s="26">
         <f t="shared" si="1"/>
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O50" s="31"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" thickBot="1">
       <c r="A51" s="1">
-        <v>49</v>
-      </c>
-      <c r="B51" s="122"/>
+        <v>62</v>
+      </c>
+      <c r="B51" s="115"/>
       <c r="C51" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="G51" s="23" t="s">
         <v>270</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="H51" s="21" t="s">
-        <v>22</v>
+      <c r="H51" s="23">
+        <v>1715260000</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J51" s="23">
         <v>1</v>
@@ -4737,1142 +4548,557 @@
         <v>24</v>
       </c>
       <c r="M51" s="26">
-        <v>0.38</v>
+        <v>2.13</v>
       </c>
       <c r="N51" s="26">
         <f t="shared" si="1"/>
-        <v>1.9</v>
-      </c>
-      <c r="O51" s="32"/>
+        <v>10.649999999999999</v>
+      </c>
+      <c r="O51" s="31"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" thickBot="1">
       <c r="A52" s="1">
-        <v>50</v>
-      </c>
-      <c r="B52" s="122"/>
+        <v>63</v>
+      </c>
+      <c r="B52" s="115"/>
       <c r="C52" s="20" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>278</v>
+        <v>19</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>272</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="H52" s="21" t="s">
-        <v>22</v>
+        <v>270</v>
+      </c>
+      <c r="H52" s="23">
+        <v>1711725</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J52" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L52" s="24" t="s">
         <v>24</v>
       </c>
       <c r="M52" s="26">
-        <v>4.2300000000000004</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="N52" s="26">
         <f t="shared" si="1"/>
-        <v>21.150000000000002</v>
+        <v>21.12</v>
       </c>
       <c r="O52" s="31"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" thickBot="1">
       <c r="A53" s="1">
-        <v>51</v>
-      </c>
-      <c r="B53" s="122"/>
-      <c r="C53" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>282</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="G53" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="H53" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B53" s="115"/>
+      <c r="C53" s="85" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="G53" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="I53" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J53" s="23">
+      <c r="I53" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J53" s="86">
         <v>1</v>
       </c>
-      <c r="K53" s="23">
+      <c r="K53" s="86">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L53" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="M53" s="26">
-        <v>1.3006</v>
-      </c>
-      <c r="N53" s="26">
-        <f t="shared" si="1"/>
-        <v>6.5030000000000001</v>
-      </c>
-      <c r="O53" s="32"/>
+      <c r="L53" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M53" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="N53" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="O53" s="31"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" thickBot="1">
       <c r="A54" s="1">
-        <v>52</v>
-      </c>
-      <c r="B54" s="122"/>
-      <c r="C54" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="F54" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="H54" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="115"/>
+      <c r="C54" s="85" t="s">
+        <v>276</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="G54" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="I54" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J54" s="23">
-        <v>1</v>
-      </c>
-      <c r="K54" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L54" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M54" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="N54" s="26">
-        <f t="shared" si="1"/>
-        <v>12</v>
+      <c r="I54" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J54" s="86">
+        <v>6</v>
+      </c>
+      <c r="K54" s="86">
+        <f t="shared" ref="K54:K61" si="2">J54*5</f>
+        <v>30</v>
+      </c>
+      <c r="L54" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M54" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="N54" s="22" t="s">
+        <v>111</v>
       </c>
       <c r="O54" s="31"/>
     </row>
     <row r="55" spans="1:15" ht="15.75" thickBot="1">
       <c r="A55" s="1">
-        <v>53</v>
-      </c>
-      <c r="B55" s="122"/>
-      <c r="C55" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="G55" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B55" s="115"/>
+      <c r="C55" s="85" t="s">
         <v>279</v>
       </c>
-      <c r="H55" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I55" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J55" s="23">
+      <c r="D55" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="G55" s="86" t="s">
+        <v>282</v>
+      </c>
+      <c r="H55" s="87"/>
+      <c r="I55" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J55" s="86">
         <v>1</v>
       </c>
-      <c r="K55" s="23">
-        <f t="shared" si="0"/>
+      <c r="K55" s="86">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L55" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M55" s="26">
-        <v>0.86</v>
-      </c>
-      <c r="N55" s="26">
-        <f t="shared" si="1"/>
-        <v>4.3</v>
+      <c r="L55" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="M55" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="N55" s="22" t="s">
+        <v>111</v>
       </c>
       <c r="O55" s="31"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" thickBot="1">
       <c r="A56" s="1">
-        <v>54</v>
-      </c>
-      <c r="B56" s="122"/>
-      <c r="C56" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="G56" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B56" s="116"/>
+      <c r="C56" s="88" t="s">
+        <v>283</v>
+      </c>
+      <c r="D56" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="H56" s="21" t="s">
+      <c r="E56" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" s="81" t="s">
+        <v>285</v>
+      </c>
+      <c r="G56" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="I56" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J56" s="23">
-        <v>1</v>
-      </c>
-      <c r="K56" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L56" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M56" s="26">
-        <v>4.01</v>
-      </c>
-      <c r="N56" s="26">
-        <f t="shared" si="1"/>
-        <v>20.049999999999997</v>
-      </c>
-      <c r="O56" s="32"/>
+      <c r="I56" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="J56" s="89">
+        <v>9</v>
+      </c>
+      <c r="K56" s="89">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="L56" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="M56" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="N56" s="81" t="s">
+        <v>111</v>
+      </c>
+      <c r="O56" s="90"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" thickBot="1">
       <c r="A57" s="1">
-        <v>55</v>
-      </c>
-      <c r="B57" s="123"/>
-      <c r="C57" s="49" t="s">
-        <v>295</v>
-      </c>
-      <c r="D57" s="50" t="s">
-        <v>296</v>
-      </c>
-      <c r="E57" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="F57" s="85" t="s">
-        <v>298</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>299</v>
-      </c>
-      <c r="H57" s="51" t="s">
-        <v>300</v>
-      </c>
-      <c r="I57" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="J57" s="51">
+        <v>68</v>
+      </c>
+      <c r="B57" s="118" t="s">
+        <v>286</v>
+      </c>
+      <c r="C57" s="91" t="s">
+        <v>287</v>
+      </c>
+      <c r="D57" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="G57" s="73" t="s">
+        <v>289</v>
+      </c>
+      <c r="H57" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="I57" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="J57" s="73">
         <v>1</v>
       </c>
-      <c r="K57" s="51">
-        <f t="shared" si="0"/>
+      <c r="K57" s="73">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L57" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="M57" s="53">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="N57" s="53">
-        <f t="shared" si="1"/>
-        <v>5.75</v>
-      </c>
-      <c r="O57" s="54"/>
+      <c r="L57" s="92" t="s">
+        <v>290</v>
+      </c>
+      <c r="M57" s="93">
+        <v>14</v>
+      </c>
+      <c r="N57" s="75">
+        <f>M57*K57</f>
+        <v>70</v>
+      </c>
+      <c r="O57" s="94"/>
     </row>
     <row r="58" spans="1:15" ht="15.75" thickBot="1">
       <c r="A58" s="1">
-        <v>56</v>
-      </c>
-      <c r="B58" s="124" t="s">
-        <v>365</v>
-      </c>
-      <c r="C58" s="88" t="s">
-        <v>301</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="E58" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" s="119"/>
+      <c r="C58" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="D58" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F58" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="H58" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="I58" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="J58" s="23">
-        <v>1</v>
-      </c>
-      <c r="K58" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L58" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="M58" s="65">
-        <v>0.47</v>
-      </c>
-      <c r="N58" s="37">
-        <f t="shared" si="1"/>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="O58" s="90"/>
+      <c r="F58" s="96" t="s">
+        <v>292</v>
+      </c>
+      <c r="G58" s="96" t="s">
+        <v>293</v>
+      </c>
+      <c r="H58" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="I58" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="J58" s="104">
+        <v>3</v>
+      </c>
+      <c r="K58" s="73">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="L58" s="92" t="s">
+        <v>290</v>
+      </c>
+      <c r="M58" s="97">
+        <v>3.35</v>
+      </c>
+      <c r="N58" s="75">
+        <f t="shared" ref="N57:N61" si="3">M58*K58</f>
+        <v>50.25</v>
+      </c>
+      <c r="O58" s="108"/>
     </row>
     <row r="59" spans="1:15" ht="15.75" thickBot="1">
       <c r="A59" s="1">
-        <v>57</v>
-      </c>
-      <c r="B59" s="122"/>
-      <c r="C59" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E59" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B59" s="119"/>
+      <c r="C59" s="98" t="s">
+        <v>294</v>
+      </c>
+      <c r="D59" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F59" s="22" t="s">
-        <v>308</v>
-      </c>
-      <c r="G59" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="I59" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J59" s="23">
+      <c r="F59" s="99" t="s">
+        <v>295</v>
+      </c>
+      <c r="G59" s="73" t="s">
+        <v>296</v>
+      </c>
+      <c r="H59" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="I59" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="J59" s="104">
         <v>1</v>
       </c>
-      <c r="K59" s="23">
-        <f t="shared" si="0"/>
+      <c r="K59" s="73">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L59" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="M59" s="26">
-        <v>1.01</v>
-      </c>
-      <c r="N59" s="26">
-        <f t="shared" si="1"/>
-        <v>5.05</v>
-      </c>
-      <c r="O59" s="31"/>
+      <c r="L59" s="92" t="s">
+        <v>290</v>
+      </c>
+      <c r="M59" s="100">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N59" s="75">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="O59" s="108"/>
     </row>
     <row r="60" spans="1:15" ht="15.75" thickBot="1">
       <c r="A60" s="1">
-        <v>58</v>
-      </c>
-      <c r="B60" s="122"/>
-      <c r="C60" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="119"/>
+      <c r="C60" s="101" t="s">
+        <v>297</v>
+      </c>
+      <c r="D60" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="73" t="s">
+        <v>298</v>
+      </c>
+      <c r="G60" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="H60" s="71" t="s">
+        <v>309</v>
+      </c>
+      <c r="I60" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="J60" s="104">
+        <v>1</v>
+      </c>
+      <c r="K60" s="73">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="L60" s="102" t="s">
+        <v>290</v>
+      </c>
+      <c r="M60" s="97">
+        <v>4.58</v>
+      </c>
+      <c r="N60" s="75">
+        <f t="shared" si="3"/>
+        <v>22.9</v>
+      </c>
+      <c r="O60" s="122" t="s">
         <v>310</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="G60" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="H60" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="I60" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J60" s="23">
-        <v>1</v>
-      </c>
-      <c r="K60" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L60" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="M60" s="26">
-        <v>0.35</v>
-      </c>
-      <c r="N60" s="26">
-        <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-      <c r="O60" s="31"/>
     </row>
     <row r="61" spans="1:15" ht="15.75" thickBot="1">
       <c r="A61" s="1">
-        <v>59</v>
-      </c>
-      <c r="B61" s="122"/>
-      <c r="C61" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="E61" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" s="120"/>
+      <c r="C61" s="103" t="s">
+        <v>299</v>
+      </c>
+      <c r="D61" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="F61" s="21" t="s">
-        <v>317</v>
-      </c>
-      <c r="G61" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J61" s="23">
+      <c r="F61" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="G61" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="H61" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="I61" s="71" t="s">
+        <v>96</v>
+      </c>
+      <c r="J61" s="104">
         <v>1</v>
       </c>
-      <c r="K61" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L61" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M61" s="26">
-        <v>0.96</v>
-      </c>
-      <c r="N61" s="26">
-        <f t="shared" si="1"/>
-        <v>4.8</v>
-      </c>
-      <c r="O61" s="32"/>
-    </row>
-    <row r="62" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A62" s="1">
-        <v>60</v>
-      </c>
-      <c r="B62" s="122"/>
-      <c r="C62" s="20" t="s">
-        <v>319</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F62" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="G62" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="H62" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="I62" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J62" s="23">
-        <v>1</v>
-      </c>
-      <c r="K62" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L62" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M62" s="26">
-        <v>0.15</v>
-      </c>
-      <c r="N62" s="26">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="O62" s="32"/>
-    </row>
-    <row r="63" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A63" s="1">
-        <v>61</v>
-      </c>
-      <c r="B63" s="122"/>
-      <c r="C63" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="E63" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="I63" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J63" s="23">
-        <v>1</v>
-      </c>
-      <c r="K63" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L63" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M63" s="26">
-        <v>0.45</v>
-      </c>
-      <c r="N63" s="26">
-        <f t="shared" si="1"/>
-        <v>2.25</v>
-      </c>
-      <c r="O63" s="31"/>
-    </row>
-    <row r="64" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A64" s="1">
-        <v>62</v>
-      </c>
-      <c r="B64" s="122"/>
-      <c r="C64" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="D64" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>330</v>
-      </c>
-      <c r="G64" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="H64" s="23">
-        <v>1715260000</v>
-      </c>
-      <c r="I64" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J64" s="23">
-        <v>1</v>
-      </c>
-      <c r="K64" s="23">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L64" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M64" s="26">
-        <v>2.13</v>
-      </c>
-      <c r="N64" s="26">
-        <f t="shared" si="1"/>
-        <v>10.649999999999999</v>
-      </c>
-      <c r="O64" s="31"/>
-    </row>
-    <row r="65" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A65" s="1">
-        <v>63</v>
-      </c>
-      <c r="B65" s="122"/>
-      <c r="C65" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="E65" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="H65" s="23">
-        <v>1711725</v>
-      </c>
-      <c r="I65" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="J65" s="23">
-        <v>2</v>
-      </c>
-      <c r="K65" s="23">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L65" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M65" s="26">
-        <v>2.1120000000000001</v>
-      </c>
-      <c r="N65" s="26">
-        <f t="shared" si="1"/>
-        <v>21.12</v>
-      </c>
-      <c r="O65" s="31"/>
-    </row>
-    <row r="66" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A66" s="1">
-        <v>64</v>
-      </c>
-      <c r="B66" s="122"/>
-      <c r="C66" s="91" t="s">
-        <v>334</v>
-      </c>
-      <c r="D66" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="E66" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="G66" s="92" t="s">
-        <v>19</v>
-      </c>
-      <c r="H66" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I66" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="J66" s="92">
-        <v>1</v>
-      </c>
-      <c r="K66" s="92">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L66" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="M66" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N66" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="O66" s="31"/>
-    </row>
-    <row r="67" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A67" s="1">
-        <v>65</v>
-      </c>
-      <c r="B67" s="122"/>
-      <c r="C67" s="91" t="s">
-        <v>337</v>
-      </c>
-      <c r="D67" s="22" t="s">
-        <v>338</v>
-      </c>
-      <c r="E67" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F67" s="22" t="s">
-        <v>339</v>
-      </c>
-      <c r="G67" s="92" t="s">
-        <v>19</v>
-      </c>
-      <c r="H67" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I67" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="J67" s="92">
-        <v>6</v>
-      </c>
-      <c r="K67" s="92">
-        <f t="shared" ref="K67:K74" si="2">J67*5</f>
-        <v>30</v>
-      </c>
-      <c r="L67" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="M67" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N67" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="O67" s="31"/>
-    </row>
-    <row r="68" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A68" s="1">
-        <v>66</v>
-      </c>
-      <c r="B68" s="122"/>
-      <c r="C68" s="91" t="s">
-        <v>340</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>341</v>
-      </c>
-      <c r="E68" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F68" s="22" t="s">
-        <v>342</v>
-      </c>
-      <c r="G68" s="92" t="s">
-        <v>343</v>
-      </c>
-      <c r="H68" s="93"/>
-      <c r="I68" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="J68" s="92">
-        <v>1</v>
-      </c>
-      <c r="K68" s="92">
+      <c r="K61" s="73">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L68" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="M68" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N68" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="O68" s="31"/>
-    </row>
-    <row r="69" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A69" s="1">
-        <v>67</v>
-      </c>
-      <c r="B69" s="123"/>
-      <c r="C69" s="94" t="s">
-        <v>344</v>
-      </c>
-      <c r="D69" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="E69" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="F69" s="85" t="s">
-        <v>346</v>
-      </c>
-      <c r="G69" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="H69" s="85" t="s">
-        <v>22</v>
-      </c>
-      <c r="I69" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="J69" s="95">
-        <v>9</v>
-      </c>
-      <c r="K69" s="95">
-        <f t="shared" si="2"/>
-        <v>45</v>
-      </c>
-      <c r="L69" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="M69" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="N69" s="85" t="s">
-        <v>112</v>
-      </c>
-      <c r="O69" s="96"/>
-    </row>
-    <row r="70" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A70" s="1">
-        <v>68</v>
-      </c>
-      <c r="B70" s="125" t="s">
-        <v>347</v>
-      </c>
-      <c r="C70" s="97" t="s">
-        <v>348</v>
-      </c>
-      <c r="D70" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E70" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" s="76" t="s">
-        <v>349</v>
-      </c>
-      <c r="G70" s="76" t="s">
-        <v>350</v>
-      </c>
-      <c r="H70" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I70" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J70" s="76">
-        <v>1</v>
-      </c>
-      <c r="K70" s="76">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L70" s="98" t="s">
-        <v>351</v>
-      </c>
-      <c r="M70" s="99">
-        <v>14</v>
-      </c>
-      <c r="N70" s="78">
-        <f t="shared" ref="N70:N74" si="3">M70*K70</f>
-        <v>70</v>
-      </c>
-      <c r="O70" s="100"/>
-    </row>
-    <row r="71" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A71" s="1">
-        <v>69</v>
-      </c>
-      <c r="B71" s="126"/>
-      <c r="C71" s="101" t="s">
-        <v>352</v>
-      </c>
-      <c r="D71" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F71" s="102" t="s">
-        <v>353</v>
-      </c>
-      <c r="G71" s="102" t="s">
-        <v>354</v>
-      </c>
-      <c r="H71" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I71" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J71" s="110">
-        <v>3</v>
-      </c>
-      <c r="K71" s="76">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="L71" s="98" t="s">
-        <v>351</v>
-      </c>
-      <c r="M71" s="103">
-        <v>3.35</v>
-      </c>
-      <c r="N71" s="78">
-        <f t="shared" si="3"/>
-        <v>50.25</v>
-      </c>
-      <c r="O71" s="115"/>
-    </row>
-    <row r="72" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A72" s="1">
-        <v>70</v>
-      </c>
-      <c r="B72" s="126"/>
-      <c r="C72" s="104" t="s">
-        <v>355</v>
-      </c>
-      <c r="D72" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E72" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F72" s="105" t="s">
-        <v>356</v>
-      </c>
-      <c r="G72" s="76" t="s">
-        <v>357</v>
-      </c>
-      <c r="H72" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I72" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J72" s="110">
-        <v>1</v>
-      </c>
-      <c r="K72" s="76">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L72" s="98" t="s">
-        <v>351</v>
-      </c>
-      <c r="M72" s="106">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="N72" s="78">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="O72" s="115"/>
-    </row>
-    <row r="73" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A73" s="1">
-        <v>71</v>
-      </c>
-      <c r="B73" s="126"/>
-      <c r="C73" s="107" t="s">
-        <v>358</v>
-      </c>
-      <c r="D73" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E73" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="76" t="s">
-        <v>359</v>
-      </c>
-      <c r="G73" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="H73" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I73" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J73" s="110">
-        <v>1</v>
-      </c>
-      <c r="K73" s="76">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L73" s="108" t="s">
-        <v>351</v>
-      </c>
-      <c r="M73" s="103">
-        <v>11.8</v>
-      </c>
-      <c r="N73" s="78">
-        <f t="shared" si="3"/>
-        <v>59</v>
-      </c>
-      <c r="O73" s="115"/>
-    </row>
-    <row r="74" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A74" s="1">
-        <v>72</v>
-      </c>
-      <c r="B74" s="127"/>
-      <c r="C74" s="109" t="s">
-        <v>360</v>
-      </c>
-      <c r="D74" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="E74" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" s="76" t="s">
-        <v>361</v>
-      </c>
-      <c r="G74" s="76" t="s">
-        <v>361</v>
-      </c>
-      <c r="H74" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="I74" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="J74" s="110">
-        <v>1</v>
-      </c>
-      <c r="K74" s="76">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L74" s="108" t="s">
-        <v>361</v>
-      </c>
-      <c r="M74" s="111">
+      <c r="L61" s="102" t="s">
+        <v>300</v>
+      </c>
+      <c r="M61" s="105">
         <v>3.95</v>
       </c>
-      <c r="N74" s="78">
+      <c r="N61" s="75">
         <f t="shared" si="3"/>
         <v>19.75</v>
       </c>
-      <c r="O74" s="115"/>
-    </row>
-    <row r="75" spans="1:15" ht="19.5" thickBot="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="7"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="7"/>
-      <c r="I75" s="119" t="s">
-        <v>362</v>
-      </c>
-      <c r="J75" s="119"/>
-      <c r="K75" s="119"/>
-      <c r="L75" s="119"/>
-      <c r="M75" s="10"/>
-      <c r="N75" s="9">
-        <f>SUM(N3:N70)</f>
-        <v>317.55750000000006</v>
-      </c>
-      <c r="O75" s="7"/>
-    </row>
-    <row r="76" spans="1:15" ht="18.75">
-      <c r="A76" s="6"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="7"/>
-      <c r="I76" s="120" t="s">
-        <v>363</v>
-      </c>
-      <c r="J76" s="120"/>
-      <c r="K76" s="120"/>
-      <c r="L76" s="120"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="10">
-        <f>N75/5</f>
-        <v>63.511500000000012</v>
-      </c>
-      <c r="O76" s="7"/>
-    </row>
-    <row r="77" spans="1:15" ht="18.75">
-      <c r="A77" s="6"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
-      <c r="F77" s="6"/>
-      <c r="G77" s="6"/>
-      <c r="H77" s="7"/>
-      <c r="I77" s="120" t="s">
-        <v>364</v>
-      </c>
-      <c r="J77" s="120"/>
-      <c r="K77" s="120"/>
-      <c r="L77" s="120"/>
-      <c r="M77" s="7"/>
-      <c r="N77" s="26">
+      <c r="O61" s="108"/>
+    </row>
+    <row r="62" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A62" s="6"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="7"/>
+      <c r="I62" s="112" t="s">
+        <v>301</v>
+      </c>
+      <c r="J62" s="112"/>
+      <c r="K62" s="112"/>
+      <c r="L62" s="112"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="9">
+        <f>SUM(N3:N61)</f>
+        <v>389.52449999999999</v>
+      </c>
+      <c r="O62" s="7"/>
+    </row>
+    <row r="63" spans="1:15" ht="18.75">
+      <c r="A63" s="6"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="7"/>
+      <c r="I63" s="113" t="s">
+        <v>302</v>
+      </c>
+      <c r="J63" s="113"/>
+      <c r="K63" s="113"/>
+      <c r="L63" s="113"/>
+      <c r="M63" s="7"/>
+      <c r="N63" s="10">
+        <f>N62/5</f>
+        <v>77.904899999999998</v>
+      </c>
+      <c r="O63" s="7"/>
+    </row>
+    <row r="64" spans="1:15" ht="18.75">
+      <c r="A64" s="6"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="113" t="s">
+        <v>303</v>
+      </c>
+      <c r="J64" s="113"/>
+      <c r="K64" s="113"/>
+      <c r="L64" s="113"/>
+      <c r="M64" s="7"/>
+      <c r="N64" s="26">
         <v>88</v>
       </c>
-      <c r="O77" s="7"/>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="A78" s="6"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="7"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="6"/>
-      <c r="M78" s="12"/>
-      <c r="O78" s="7"/>
+      <c r="O64" s="7"/>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="6"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="7"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="7"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="12"/>
+      <c r="O65" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="I75:L75"/>
-    <mergeCell ref="I76:L76"/>
-    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="I62:L62"/>
+    <mergeCell ref="I63:L63"/>
+    <mergeCell ref="I64:L64"/>
     <mergeCell ref="B3:B16"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="B30:B47"/>
-    <mergeCell ref="B48:B57"/>
-    <mergeCell ref="B58:B69"/>
-    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B27:B39"/>
+    <mergeCell ref="B40:B45"/>
+    <mergeCell ref="B46:B56"/>
+    <mergeCell ref="B57:B61"/>
   </mergeCells>
   <conditionalFormatting sqref="J7">
     <cfRule type="colorScale" priority="30">
@@ -5910,7 +5136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N76">
+  <conditionalFormatting sqref="N63">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -5948,18 +5174,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J19:J22">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
+  <conditionalFormatting sqref="J57:J61">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5969,30 +5185,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J23:J24">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J70:J74">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -6003,32 +5195,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N65">
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF638EC6"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{29C5D989-E8D6-4FA3-89BC-72179293C40F}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N70:N74">
+  <conditionalFormatting sqref="N57:N61">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -6042,8 +5210,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:K3 K18:K74 J4:J6 K4:K16">
-    <cfRule type="colorScale" priority="33">
+  <conditionalFormatting sqref="J11:J16 J18">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6053,9 +5221,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K16 K18:K74">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6066,29 +5232,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J16 J18">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25:J28 J69 J62 J66:J67 J46:J47">
+  <conditionalFormatting sqref="J23:J25 J56 J49 J53:J54 J39">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -6100,7 +5244,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J25:J33 J69 J62 J46:J52 J66:J67">
+  <conditionalFormatting sqref="J23:J29 J56 J49 J39:J41 J53:J54">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -6112,7 +5256,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29 J48">
+  <conditionalFormatting sqref="J40 J26">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -6124,31 +5268,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J30 J49">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J32 J50:J51">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33 J52">
+  <conditionalFormatting sqref="J41">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -6160,18 +5280,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J38 J53:J60">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="J50:J51 J34:J37 J55 J48">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6181,8 +5291,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J39:J44 J63:J64 J68 J61">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -6193,7 +5301,9 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="10">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J52 J38">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6203,8 +5313,6 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J45 J65">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -6215,18 +5323,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M75">
+  <conditionalFormatting sqref="M62">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -6240,7 +5338,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N77">
+  <conditionalFormatting sqref="N64">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -6252,6 +5350,134 @@
           <x14:id>{603E608C-8C58-42D3-9EDD-50BEF2094DB9}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:J21">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
+    <cfRule type="colorScale" priority="175">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28:J29">
+    <cfRule type="colorScale" priority="176">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J42:J47 J30:J33">
+    <cfRule type="colorScale" priority="241">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="242">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3:N52">
+    <cfRule type="dataBar" priority="247">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{29C5D989-E8D6-4FA3-89BC-72179293C40F}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3:K3 K18:K61 J4:J6 K4:K16">
+    <cfRule type="colorScale" priority="249">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3:K16 K18:K61">
+    <cfRule type="colorScale" priority="254">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -6269,59 +5495,46 @@
     <hyperlink ref="L15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="L16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="L18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="L25" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="L27" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="L31" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="L32" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="L33" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="L34" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="L35" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="L36" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="L37" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="L38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="L39" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="L40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="L45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="L46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="L51" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="L53" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="L56" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="L57" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="L61" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="L30" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="L43" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="L44" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="L19" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="L20" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="L21" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="L22" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L23" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="L29" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="L48" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="L50" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="L4" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="L26" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="L28" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="L49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="L52" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="L54" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="L55" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="L59" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="L60" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="L63" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="L64" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="L65" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L62" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="L17" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="L41" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="L42" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="L47" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="L58" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="L24" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="L74" r:id="rId64" location="technical-details" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="L24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="L28" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="L29" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="L30" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="L31" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="L32" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="L33" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="L34" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="L35" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="L38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="L39" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="L42" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="L45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="L48" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="L27" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="L19" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="L20" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="L21" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="L26" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="L40" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="L4" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="L25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="L41" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="L43" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="L44" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="L47" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="L50" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="L51" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="L52" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="L49" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="L17" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="L36" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="L37" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="L46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="L61" r:id="rId49" location="technical-details" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="L22" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="L23" r:id="rId51" display="Digikey" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId65"/>
+  <pageSetup orientation="portrait" r:id="rId52"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -6336,7 +5549,46 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N76</xm:sqref>
+          <xm:sqref>N63</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C4DCDE22-C4C3-4E18-86E0-AE0957909D63}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N57:N61</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{64D35CED-CB77-4E7D-8609-DD7C9579E340}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFD6007B"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>M62</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{603E608C-8C58-42D3-9EDD-50BEF2094DB9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>N64</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{29C5D989-E8D6-4FA3-89BC-72179293C40F}">
@@ -6349,46 +5601,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N65</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C4DCDE22-C4C3-4E18-86E0-AE0957909D63}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>N70:N74</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{64D35CED-CB77-4E7D-8609-DD7C9579E340}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFD6007B"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>M75</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{603E608C-8C58-42D3-9EDD-50BEF2094DB9}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF638EC6"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>N77</xm:sqref>
+          <xm:sqref>N3:N52</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverable/Main_Board/BOM/(5 Board)Digikey_Main_Board-BOM.xlsx
+++ b/Deliverable/Main_Board/BOM/(5 Board)Digikey_Main_Board-BOM.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DCEE96-A114-4258-9E60-ECE5F26B1036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FD4D53-1B78-4B70-A079-1142B38CF74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,10 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="311">
-  <si>
-    <t>Bill of Material (BOM) for Grant</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="301">
   <si>
     <t>S. No.</t>
   </si>
@@ -628,36 +625,6 @@
     <t>1K</t>
   </si>
   <si>
-    <t>RES SMD 100K OHM 1% 1/5W 0402</t>
-  </si>
-  <si>
-    <t>R28, R30, R31, R32</t>
-  </si>
-  <si>
-    <t>ERJPA2F1003X</t>
-  </si>
-  <si>
-    <t>RC0402JR-07100KL</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>RES SMD 4.7K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>R29</t>
-  </si>
-  <si>
-    <t>Res0603</t>
-  </si>
-  <si>
-    <t>RC0603FR-074K7L</t>
-  </si>
-  <si>
-    <t>4.7K</t>
-  </si>
-  <si>
     <t>RES SMD 118K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -896,9 +863,6 @@
     <t>Solder Bridge ON</t>
   </si>
   <si>
-    <t>SB2, SB3, SB16, SB17, SB18, SB19, SB20, SB21, SB_ZD1</t>
-  </si>
-  <si>
     <t>Solder Bridge</t>
   </si>
   <si>
@@ -975,6 +939,12 @@
   </si>
   <si>
     <t>IP65 rating</t>
+  </si>
+  <si>
+    <t>SB3, SB21, SB_ZD1</t>
+  </si>
+  <si>
+    <t>Bill of Material (BOM) for Grant Main Board</t>
   </si>
 </sst>
 </file>
@@ -988,7 +958,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,7 +971,7 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1009,7 +979,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1017,7 +987,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1025,13 +995,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1039,7 +1009,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1047,7 +1017,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1055,6 +1025,7 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1141,13 +1112,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1391,17 +1355,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -1609,6 +1562,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1618,7 +1584,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1671,10 +1637,10 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1698,7 +1664,7 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1707,13 +1673,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1723,7 +1689,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1738,26 +1704,23 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1773,7 +1736,7 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1789,53 +1752,35 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1856,10 +1801,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1875,52 +1820,49 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="19" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="19" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1929,17 +1871,44 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1954,7 +1923,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1964,12 +1933,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2248,7 +2211,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O65"/>
+  <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
@@ -2268,114 +2231,114 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="110"/>
-      <c r="C1" s="110"/>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
-      <c r="I1" s="110"/>
-      <c r="J1" s="110"/>
-      <c r="K1" s="110"/>
-      <c r="L1" s="110"/>
-      <c r="M1" s="110"/>
-      <c r="N1" s="110"/>
-      <c r="O1" s="111"/>
+      <c r="A1" s="110" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="112"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" thickBot="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="E3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="I3" s="14" t="s">
         <v>22</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>23</v>
       </c>
       <c r="J3" s="15">
         <v>1</v>
       </c>
       <c r="K3" s="15">
-        <f t="shared" ref="K3:K53" si="0">J3*5</f>
+        <f t="shared" ref="K3:K51" si="0">J3*5</f>
         <v>5</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M3" s="17">
         <v>0.43</v>
       </c>
       <c r="N3" s="18">
-        <f t="shared" ref="N3:N52" si="1">M3*K3</f>
+        <f t="shared" ref="N3:N50" si="1">M3*K3</f>
         <v>2.15</v>
       </c>
       <c r="O3" s="19"/>
@@ -2384,27 +2347,27 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="115"/>
+      <c r="B4" s="116"/>
       <c r="C4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="E4" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="22" t="s">
+      <c r="G4" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="H4" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="I4" s="21" t="s">
         <v>29</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>30</v>
       </c>
       <c r="J4" s="23">
         <v>1</v>
@@ -2414,7 +2377,7 @@
         <v>5</v>
       </c>
       <c r="L4" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M4" s="25">
         <v>0.47</v>
@@ -2429,27 +2392,27 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="115"/>
+      <c r="B5" s="116"/>
       <c r="C5" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="98" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="106" t="s">
-        <v>305</v>
-      </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="G5" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="H5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="21" t="s">
         <v>34</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>35</v>
       </c>
       <c r="J5" s="23">
         <v>14</v>
@@ -2459,7 +2422,7 @@
         <v>70</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M5" s="25">
         <v>1.5800000000000002E-2</v>
@@ -2474,27 +2437,27 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="115"/>
+      <c r="B6" s="116"/>
       <c r="C6" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="E6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="F6" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="H6" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="21" t="s">
         <v>40</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="21" t="s">
-        <v>41</v>
       </c>
       <c r="J6" s="23">
         <v>2</v>
@@ -2504,7 +2467,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M6" s="26">
         <v>0.30199999999999999</v>
@@ -2519,27 +2482,27 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="115"/>
+      <c r="B7" s="116"/>
       <c r="C7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="21" t="s">
+      <c r="G7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="H7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="21" t="s">
         <v>45</v>
-      </c>
-      <c r="H7" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="J7" s="23">
         <v>2</v>
@@ -2549,7 +2512,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M7" s="26">
         <v>0.378</v>
@@ -2564,27 +2527,27 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="115"/>
+      <c r="B8" s="116"/>
       <c r="C8" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="E8" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="F8" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="G8" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="H8" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="21" t="s">
         <v>51</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>52</v>
       </c>
       <c r="J8" s="23">
         <v>1</v>
@@ -2594,7 +2557,7 @@
         <v>5</v>
       </c>
       <c r="L8" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M8" s="26">
         <v>0.11</v>
@@ -2609,27 +2572,27 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="115"/>
+      <c r="B9" s="116"/>
       <c r="C9" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="E9" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="F9" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="G9" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="21" t="s">
+      <c r="I9" s="21" t="s">
         <v>57</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>58</v>
       </c>
       <c r="J9" s="23">
         <v>4</v>
@@ -2639,7 +2602,7 @@
         <v>20</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M9" s="26">
         <v>2.5999999999999999E-2</v>
@@ -2654,27 +2617,27 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="115"/>
+      <c r="B10" s="116"/>
       <c r="C10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="21" t="s">
+      <c r="G10" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="H10" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="21" t="s">
         <v>62</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>63</v>
       </c>
       <c r="J10" s="23">
         <v>1</v>
@@ -2684,7 +2647,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M10" s="26">
         <v>0.11</v>
@@ -2699,27 +2662,27 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="115"/>
+      <c r="B11" s="116"/>
       <c r="C11" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="F11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="G11" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="H11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="21" t="s">
         <v>68</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>69</v>
       </c>
       <c r="J11" s="23">
         <v>1</v>
@@ -2729,7 +2692,7 @@
         <v>5</v>
       </c>
       <c r="L11" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M11" s="26">
         <v>0.44</v>
@@ -2744,27 +2707,27 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="115"/>
+      <c r="B12" s="116"/>
       <c r="C12" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="E12" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="21" t="s">
+      <c r="G12" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="H12" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="21" t="s">
         <v>74</v>
-      </c>
-      <c r="H12" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>75</v>
       </c>
       <c r="J12" s="23">
         <v>1</v>
@@ -2774,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M12" s="33">
         <v>0.6411</v>
@@ -2789,27 +2752,27 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="115"/>
+      <c r="B13" s="116"/>
       <c r="C13" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="E13" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="21" t="s">
+      <c r="G13" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="H13" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="21" t="s">
         <v>80</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>81</v>
       </c>
       <c r="J13" s="23">
         <v>1</v>
@@ -2819,7 +2782,7 @@
         <v>5</v>
       </c>
       <c r="L13" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M13" s="26">
         <v>0.25900000000000001</v>
@@ -2834,27 +2797,27 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="115"/>
+      <c r="B14" s="116"/>
       <c r="C14" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="E14" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="21" t="s">
+      <c r="G14" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="H14" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="21" t="s">
         <v>85</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>86</v>
       </c>
       <c r="J14" s="23">
         <v>1</v>
@@ -2864,7 +2827,7 @@
         <v>5</v>
       </c>
       <c r="L14" s="35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M14" s="26">
         <v>0.156</v>
@@ -2879,27 +2842,27 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="115"/>
+      <c r="B15" s="116"/>
       <c r="C15" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="21" t="s">
+      <c r="G15" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="H15" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="21" t="s">
         <v>90</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>91</v>
       </c>
       <c r="J15" s="36">
         <v>1</v>
@@ -2909,7 +2872,7 @@
         <v>5</v>
       </c>
       <c r="L15" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M15" s="37">
         <v>0.52</v>
@@ -2924,27 +2887,27 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="115"/>
+      <c r="B16" s="116"/>
       <c r="C16" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="E16" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="39" t="s">
+      <c r="G16" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="H16" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="39" t="s">
+      <c r="I16" s="39" t="s">
         <v>96</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>97</v>
       </c>
       <c r="J16" s="34">
         <v>1</v>
@@ -2954,7 +2917,7 @@
         <v>5</v>
       </c>
       <c r="L16" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M16" s="42">
         <v>0.1</v>
@@ -2969,29 +2932,29 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="115" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="D17" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="E17" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="F17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="G17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>103</v>
-      </c>
       <c r="H17" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" s="15">
         <v>1</v>
@@ -3000,90 +2963,90 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L17" s="107" t="s">
-        <v>104</v>
-      </c>
-      <c r="M17" s="46">
+      <c r="L17" s="99" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" s="45">
         <v>0.5</v>
       </c>
-      <c r="N17" s="47">
+      <c r="N17" s="46">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="O17" s="48"/>
+      <c r="O17" s="47"/>
     </row>
     <row r="18" spans="1:15" ht="15.75" thickBot="1">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="116"/>
-      <c r="C18" s="49" t="s">
+      <c r="B18" s="117"/>
+      <c r="C18" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="50" t="s">
+      <c r="E18" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="F18" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="G18" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="G18" s="51" t="s">
+      <c r="H18" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="H18" s="50" t="s">
+      <c r="I18" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" s="51">
+      <c r="J18" s="50">
         <v>2</v>
       </c>
-      <c r="K18" s="51">
+      <c r="K18" s="50">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L18" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="M18" s="53">
+      <c r="L18" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="52">
         <v>0.32200000000000001</v>
       </c>
-      <c r="N18" s="53">
+      <c r="N18" s="52">
         <f t="shared" si="1"/>
         <v>3.22</v>
       </c>
-      <c r="O18" s="54"/>
+      <c r="O18" s="53"/>
     </row>
     <row r="19" spans="1:15" ht="16.5" thickBot="1">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="C19" s="55" t="s">
+      <c r="D19" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="E19" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="D19" s="56" t="s">
-        <v>306</v>
-      </c>
-      <c r="E19" s="56" t="s">
+      <c r="F19" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="57" t="s">
+      <c r="G19" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="H19" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="H19" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="I19" s="56" t="s">
-        <v>111</v>
+      <c r="I19" s="55" t="s">
+        <v>110</v>
       </c>
       <c r="J19" s="40">
         <v>1</v>
@@ -3092,45 +3055,45 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L19" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="59">
+      <c r="L19" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="58">
         <v>0.32200000000000001</v>
       </c>
-      <c r="N19" s="59">
+      <c r="N19" s="58">
         <f t="shared" si="1"/>
         <v>1.61</v>
       </c>
-      <c r="O19" s="60"/>
+      <c r="O19" s="59"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="114" t="s">
+      <c r="B20" s="115" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D20" s="102" t="s">
         <v>119</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="E20" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="F20" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="G20" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="H20" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J20" s="15">
         <v>1</v>
@@ -3140,42 +3103,42 @@
         <v>5</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="47">
+        <v>23</v>
+      </c>
+      <c r="M20" s="46">
         <v>0.52</v>
       </c>
-      <c r="N20" s="47">
+      <c r="N20" s="46">
         <f t="shared" si="1"/>
         <v>2.6</v>
       </c>
-      <c r="O20" s="61"/>
+      <c r="O20" s="60"/>
     </row>
     <row r="21" spans="1:15" ht="15.75" thickBot="1">
       <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="115"/>
+        <v>19</v>
+      </c>
+      <c r="B21" s="116"/>
       <c r="C21" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="103" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="E21" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="21" t="s">
+      <c r="G21" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G21" s="23" t="s">
-        <v>127</v>
-      </c>
       <c r="H21" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="62" t="s">
-        <v>111</v>
+        <v>21</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>110</v>
       </c>
       <c r="J21" s="23">
         <v>1</v>
@@ -3185,7 +3148,7 @@
         <v>5</v>
       </c>
       <c r="L21" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M21" s="26">
         <v>0.67</v>
@@ -3198,215 +3161,215 @@
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1">
       <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" s="116"/>
+      <c r="C22" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="109" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="115"/>
-      <c r="C22" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="G22" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="J22" s="23">
+      <c r="I22" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="J22" s="34">
         <v>1</v>
       </c>
-      <c r="K22" s="23">
+      <c r="K22" s="34">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L22" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="26">
+      <c r="L22" s="104" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="37">
         <v>0.55000000000000004</v>
       </c>
-      <c r="N22" s="26">
+      <c r="N22" s="37">
         <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
-      <c r="O22" s="31"/>
+      <c r="O22" s="105"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1">
       <c r="A23" s="1">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B23" s="115" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="65" t="s">
+      <c r="D23" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="E23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="121" t="s">
+      <c r="G23" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="G23" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="J23" s="66">
+      <c r="H23" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J23" s="15">
         <v>1</v>
       </c>
-      <c r="K23" s="66">
+      <c r="K23" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L23" s="67" t="s">
-        <v>290</v>
-      </c>
-      <c r="M23" s="68">
+      <c r="L23" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="M23" s="46">
         <v>1.5</v>
       </c>
-      <c r="N23" s="68">
+      <c r="N23" s="46">
         <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
-      <c r="O23" s="31"/>
+      <c r="O23" s="60"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1">
       <c r="A24" s="1">
-        <v>25</v>
-      </c>
-      <c r="B24" s="115"/>
-      <c r="C24" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="117"/>
+      <c r="C24" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="D24" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="E24" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="E24" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="39" t="s">
+      <c r="G24" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="G24" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="H24" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="J24" s="34">
+      <c r="H24" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="107" t="s">
+        <v>110</v>
+      </c>
+      <c r="J24" s="50">
         <v>1</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L24" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="37">
+      <c r="L24" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="M24" s="52">
         <v>1.01</v>
       </c>
-      <c r="N24" s="37">
+      <c r="N24" s="52">
         <f t="shared" si="1"/>
         <v>5.05</v>
       </c>
-      <c r="O24" s="43"/>
+      <c r="O24" s="53"/>
     </row>
     <row r="25" spans="1:15" ht="16.5" thickBot="1">
       <c r="A25" s="1">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="70" t="s">
+      <c r="D25" s="108" t="s">
         <v>141</v>
       </c>
-      <c r="D25" s="71" t="s">
+      <c r="E25" s="64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="E25" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="72" t="s">
+      <c r="G25" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="G25" s="73" t="s">
+      <c r="H25" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="H25" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="I25" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="J25" s="73">
+      <c r="I25" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="J25" s="66">
         <v>1</v>
       </c>
-      <c r="K25" s="73">
+      <c r="K25" s="66">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L25" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="M25" s="75">
+      <c r="L25" s="67" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="68">
         <v>0.68</v>
       </c>
-      <c r="N25" s="75">
+      <c r="N25" s="68">
         <f t="shared" si="1"/>
         <v>3.4000000000000004</v>
       </c>
-      <c r="O25" s="76"/>
+      <c r="O25" s="69"/>
     </row>
     <row r="26" spans="1:15" ht="16.5" thickBot="1">
       <c r="A26" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="D26" s="55" t="s">
         <v>147</v>
       </c>
-      <c r="D26" s="56" t="s">
+      <c r="E26" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="55" t="s">
         <v>148</v>
       </c>
-      <c r="E26" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="56" t="s">
+      <c r="G26" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="G26" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="H26" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="56" t="s">
-        <v>111</v>
+      <c r="H26" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="55" t="s">
+        <v>110</v>
       </c>
       <c r="J26" s="40">
         <v>2</v>
@@ -3415,45 +3378,45 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L26" s="58" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="59">
+      <c r="L26" s="57" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="58">
         <v>0.65400000000000003</v>
       </c>
-      <c r="N26" s="59">
+      <c r="N26" s="58">
         <f t="shared" si="1"/>
         <v>6.54</v>
       </c>
-      <c r="O26" s="60"/>
+      <c r="O26" s="59"/>
     </row>
     <row r="27" spans="1:15" ht="15.75" thickBot="1">
       <c r="A27" s="1">
-        <v>28</v>
-      </c>
-      <c r="B27" s="114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="115" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="D27" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="F27" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="F27" s="78" t="s">
+      <c r="G27" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="G27" s="15" t="s">
+      <c r="H27" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="I27" s="14" t="s">
         <v>157</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>158</v>
       </c>
       <c r="J27" s="15">
         <v>1</v>
@@ -3462,43 +3425,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="79" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="47">
+      <c r="L27" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="M27" s="46">
         <v>0.1</v>
       </c>
-      <c r="N27" s="47">
+      <c r="N27" s="46">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="O27" s="48"/>
+      <c r="O27" s="47"/>
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1">
       <c r="A28" s="1">
-        <v>29</v>
-      </c>
-      <c r="B28" s="115"/>
+        <v>26</v>
+      </c>
+      <c r="B28" s="116"/>
       <c r="C28" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D28" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="E28" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="F28" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="G28" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="H28" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="21" t="s">
         <v>163</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="21" t="s">
-        <v>164</v>
       </c>
       <c r="J28" s="23">
         <v>1</v>
@@ -3508,7 +3471,7 @@
         <v>5</v>
       </c>
       <c r="L28" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M28" s="26">
         <v>0.1</v>
@@ -3521,29 +3484,29 @@
     </row>
     <row r="29" spans="1:15" ht="15.75" thickBot="1">
       <c r="A29" s="1">
-        <v>30</v>
-      </c>
-      <c r="B29" s="115"/>
+        <v>27</v>
+      </c>
+      <c r="B29" s="116"/>
       <c r="C29" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F29" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="D29" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="E29" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="21" t="s">
+      <c r="G29" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="21" t="s">
         <v>166</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H29" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>167</v>
       </c>
       <c r="J29" s="23">
         <v>5</v>
@@ -3553,7 +3516,7 @@
         <v>25</v>
       </c>
       <c r="L29" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M29" s="26">
         <v>1.2999999999999999E-2</v>
@@ -3564,31 +3527,31 @@
       </c>
       <c r="O29" s="32"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1">
+    <row r="30" spans="1:15" ht="26.25" thickBot="1">
       <c r="A30" s="1">
-        <v>33</v>
-      </c>
-      <c r="B30" s="115"/>
+        <v>28</v>
+      </c>
+      <c r="B30" s="116"/>
       <c r="C30" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="E30" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="E30" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="G30" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="H30" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="H30" s="80" t="s">
+      <c r="I30" s="21" t="s">
         <v>172</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>173</v>
       </c>
       <c r="J30" s="23">
         <v>9</v>
@@ -3598,7 +3561,7 @@
         <v>45</v>
       </c>
       <c r="L30" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M30" s="26">
         <v>0.223</v>
@@ -3611,29 +3574,29 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickBot="1">
       <c r="A31" s="1">
-        <v>34</v>
-      </c>
-      <c r="B31" s="115"/>
+        <v>29</v>
+      </c>
+      <c r="B31" s="116"/>
       <c r="C31" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D31" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="E31" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="E31" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" s="21" t="s">
+      <c r="G31" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="21" t="s">
         <v>176</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="21" t="s">
-        <v>177</v>
       </c>
       <c r="J31" s="23">
         <v>1</v>
@@ -3643,7 +3606,7 @@
         <v>5</v>
       </c>
       <c r="L31" s="24" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M31" s="26">
         <v>0.10100000000000001</v>
@@ -3656,29 +3619,29 @@
     </row>
     <row r="32" spans="1:15" ht="15.75" thickBot="1">
       <c r="A32" s="1">
-        <v>35</v>
-      </c>
-      <c r="B32" s="115"/>
+        <v>30</v>
+      </c>
+      <c r="B32" s="116"/>
       <c r="C32" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D32" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="E32" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F32" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="E32" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F32" s="22" t="s">
+      <c r="G32" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="H32" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="G32" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H32" s="23" t="s">
+      <c r="I32" s="21" t="s">
         <v>181</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>182</v>
       </c>
       <c r="J32" s="23">
         <v>1</v>
@@ -3688,7 +3651,7 @@
         <v>5</v>
       </c>
       <c r="L32" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M32" s="26">
         <v>0.1</v>
@@ -3701,29 +3664,29 @@
     </row>
     <row r="33" spans="1:15" ht="15.75" thickBot="1">
       <c r="A33" s="1">
-        <v>36</v>
-      </c>
-      <c r="B33" s="115"/>
+        <v>31</v>
+      </c>
+      <c r="B33" s="116"/>
       <c r="C33" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="D33" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="E33" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F33" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F33" s="22" t="s">
+      <c r="G33" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H33" s="23" t="s">
+      <c r="I33" s="21" t="s">
         <v>186</v>
-      </c>
-      <c r="I33" s="21" t="s">
-        <v>187</v>
       </c>
       <c r="J33" s="23">
         <v>4</v>
@@ -3733,7 +3696,7 @@
         <v>20</v>
       </c>
       <c r="L33" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M33" s="26">
         <v>1.2999999999999999E-2</v>
@@ -3746,29 +3709,29 @@
     </row>
     <row r="34" spans="1:15" ht="15.75" thickBot="1">
       <c r="A34" s="1">
-        <v>37</v>
-      </c>
-      <c r="B34" s="115"/>
+        <v>32</v>
+      </c>
+      <c r="B34" s="116"/>
       <c r="C34" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D34" s="21" t="s">
+      <c r="E34" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F34" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="E34" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F34" s="21" t="s">
+      <c r="G34" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="21" t="s">
         <v>190</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>191</v>
       </c>
       <c r="J34" s="23">
         <v>3</v>
@@ -3778,7 +3741,7 @@
         <v>15</v>
       </c>
       <c r="L34" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M34" s="26">
         <v>1.6E-2</v>
@@ -3791,29 +3754,29 @@
     </row>
     <row r="35" spans="1:15" ht="15.75" thickBot="1">
       <c r="A35" s="1">
-        <v>38</v>
-      </c>
-      <c r="B35" s="115"/>
+        <v>33</v>
+      </c>
+      <c r="B35" s="116"/>
       <c r="C35" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F35" s="22" t="s">
+      <c r="G35" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="G35" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H35" s="23" t="s">
+      <c r="I35" s="21" t="s">
         <v>194</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>195</v>
       </c>
       <c r="J35" s="23">
         <v>1</v>
@@ -3823,7 +3786,7 @@
         <v>5</v>
       </c>
       <c r="L35" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M35" s="26">
         <v>0.1</v>
@@ -3836,72 +3799,74 @@
     </row>
     <row r="36" spans="1:15" ht="15.75" thickBot="1">
       <c r="A36" s="1">
-        <v>39</v>
-      </c>
-      <c r="B36" s="115"/>
-      <c r="C36" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="116"/>
+      <c r="C36" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="E36" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F36" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="E36" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F36" s="22" t="s">
+      <c r="G36" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="G36" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>200</v>
-      </c>
       <c r="J36" s="23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K36" s="23">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="L36" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M36" s="64">
-        <v>1.2999999999999999E-2</v>
+        <v>23</v>
+      </c>
+      <c r="M36" s="26">
+        <v>0.1</v>
       </c>
       <c r="N36" s="26">
         <f t="shared" si="1"/>
-        <v>0.26</v>
-      </c>
-      <c r="O36" s="31"/>
+        <v>0.5</v>
+      </c>
+      <c r="O36" s="32"/>
     </row>
     <row r="37" spans="1:15" ht="15.75" thickBot="1">
       <c r="A37" s="1">
-        <v>40</v>
-      </c>
-      <c r="B37" s="115"/>
-      <c r="C37" s="63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="116"/>
+      <c r="C37" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F37" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="G37" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="21" t="s">
         <v>202</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="G37" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23" t="s">
-        <v>205</v>
       </c>
       <c r="J37" s="23">
         <v>1</v>
@@ -3911,9 +3876,9 @@
         <v>5</v>
       </c>
       <c r="L37" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M37" s="64">
+        <v>23</v>
+      </c>
+      <c r="M37" s="26">
         <v>0.1</v>
       </c>
       <c r="N37" s="26">
@@ -3924,54 +3889,56 @@
     </row>
     <row r="38" spans="1:15" ht="15.75" thickBot="1">
       <c r="A38" s="1">
-        <v>43</v>
-      </c>
-      <c r="B38" s="115"/>
-      <c r="C38" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="115" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="E38" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="F38" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="E38" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="F38" s="21" t="s">
+      <c r="G38" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="G38" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="H38" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="J38" s="23">
+      <c r="H38" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="J38" s="15">
         <v>1</v>
       </c>
-      <c r="K38" s="23">
+      <c r="K38" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L38" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M38" s="26">
-        <v>0.1</v>
-      </c>
-      <c r="N38" s="26">
+      <c r="L38" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" s="46">
+        <v>1.2</v>
+      </c>
+      <c r="N38" s="46">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O38" s="32"/>
+        <v>6</v>
+      </c>
+      <c r="O38" s="60"/>
     </row>
     <row r="39" spans="1:15" ht="15.75" thickBot="1">
       <c r="A39" s="1">
-        <v>44</v>
-      </c>
-      <c r="B39" s="115"/>
+        <v>37</v>
+      </c>
+      <c r="B39" s="116"/>
       <c r="C39" s="20" t="s">
         <v>210</v>
       </c>
@@ -3979,19 +3946,19 @@
         <v>211</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I39" s="21" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="J39" s="23">
         <v>1</v>
@@ -4001,89 +3968,87 @@
         <v>5</v>
       </c>
       <c r="L39" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M39" s="26">
-        <v>0.1</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="N39" s="26">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="O39" s="32"/>
+        <v>21.150000000000002</v>
+      </c>
+      <c r="O39" s="31"/>
     </row>
     <row r="40" spans="1:15" ht="15.75" thickBot="1">
       <c r="A40" s="1">
-        <v>46</v>
-      </c>
-      <c r="B40" s="114" t="s">
-        <v>214</v>
-      </c>
-      <c r="C40" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="116"/>
+      <c r="C40" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="F40" s="14" t="s">
+      <c r="F40" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="G40" s="15" t="s">
+      <c r="G40" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="H40" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="J40" s="15">
+      <c r="H40" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I40" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="J40" s="23">
         <v>1</v>
       </c>
-      <c r="K40" s="15">
+      <c r="K40" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L40" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="M40" s="47">
-        <v>1.2</v>
-      </c>
-      <c r="N40" s="47">
+      <c r="L40" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="M40" s="26">
+        <v>1.3006</v>
+      </c>
+      <c r="N40" s="26">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="O40" s="61"/>
+        <v>6.5030000000000001</v>
+      </c>
+      <c r="O40" s="32"/>
     </row>
     <row r="41" spans="1:15" ht="15.75" thickBot="1">
       <c r="A41" s="1">
-        <v>50</v>
-      </c>
-      <c r="B41" s="115"/>
+        <v>39</v>
+      </c>
+      <c r="B41" s="116"/>
       <c r="C41" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="E41" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="F41" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>224</v>
-      </c>
       <c r="G41" s="23" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I41" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J41" s="23">
         <v>1</v>
@@ -4093,42 +4058,42 @@
         <v>5</v>
       </c>
       <c r="L41" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M41" s="26">
-        <v>4.2300000000000004</v>
+        <v>2.4</v>
       </c>
       <c r="N41" s="26">
         <f t="shared" si="1"/>
-        <v>21.150000000000002</v>
+        <v>12</v>
       </c>
       <c r="O41" s="31"/>
     </row>
     <row r="42" spans="1:15" ht="15.75" thickBot="1">
       <c r="A42" s="1">
-        <v>51</v>
-      </c>
-      <c r="B42" s="115"/>
+        <v>40</v>
+      </c>
+      <c r="B42" s="116"/>
       <c r="C42" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="D42" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>229</v>
-      </c>
       <c r="G42" s="23" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="H42" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I42" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J42" s="23">
         <v>1</v>
@@ -4138,87 +4103,89 @@
         <v>5</v>
       </c>
       <c r="L42" s="24" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="M42" s="26">
-        <v>1.3006</v>
+        <v>0.86</v>
       </c>
       <c r="N42" s="26">
         <f t="shared" si="1"/>
-        <v>6.5030000000000001</v>
-      </c>
-      <c r="O42" s="32"/>
+        <v>4.3</v>
+      </c>
+      <c r="O42" s="31"/>
     </row>
     <row r="43" spans="1:15" ht="15.75" thickBot="1">
       <c r="A43" s="1">
-        <v>52</v>
-      </c>
-      <c r="B43" s="115"/>
-      <c r="C43" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="117"/>
+      <c r="C43" s="48" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="F43" s="74" t="s">
+        <v>230</v>
+      </c>
+      <c r="G43" s="50" t="s">
         <v>231</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="H43" s="50" t="s">
         <v>232</v>
       </c>
-      <c r="E43" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="G43" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="H43" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I43" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="J43" s="23">
+      <c r="I43" s="49" t="s">
+        <v>110</v>
+      </c>
+      <c r="J43" s="50">
         <v>1</v>
       </c>
-      <c r="K43" s="23">
+      <c r="K43" s="50">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L43" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M43" s="26">
-        <v>2.4</v>
-      </c>
-      <c r="N43" s="26">
+      <c r="L43" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="52">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="N43" s="52">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="O43" s="31"/>
+        <v>5.75</v>
+      </c>
+      <c r="O43" s="53"/>
     </row>
     <row r="44" spans="1:15" ht="15.75" thickBot="1">
       <c r="A44" s="1">
-        <v>53</v>
-      </c>
-      <c r="B44" s="115"/>
-      <c r="C44" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="118" t="s">
+        <v>292</v>
+      </c>
+      <c r="C44" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="G44" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="E44" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="F44" s="21" t="s">
+      <c r="H44" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="G44" s="23" t="s">
-        <v>225</v>
-      </c>
-      <c r="H44" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I44" s="21" t="s">
-        <v>111</v>
+      <c r="I44" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="J44" s="23">
         <v>1</v>
@@ -4227,90 +4194,88 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L44" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M44" s="26">
-        <v>0.86</v>
-      </c>
-      <c r="N44" s="26">
+      <c r="L44" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="62">
+        <v>0.47</v>
+      </c>
+      <c r="N44" s="37">
         <f t="shared" si="1"/>
-        <v>4.3</v>
-      </c>
-      <c r="O44" s="31"/>
+        <v>2.3499999999999996</v>
+      </c>
+      <c r="O44" s="77"/>
     </row>
     <row r="45" spans="1:15" ht="15.75" thickBot="1">
       <c r="A45" s="1">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B45" s="116"/>
-      <c r="C45" s="49" t="s">
+      <c r="C45" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="D45" s="50" t="s">
+      <c r="D45" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="E45" s="50" t="s">
+      <c r="E45" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="F45" s="81" t="s">
+      <c r="G45" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="G45" s="51" t="s">
+      <c r="H45" s="23" t="s">
         <v>242</v>
       </c>
-      <c r="H45" s="51" t="s">
-        <v>243</v>
-      </c>
-      <c r="I45" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="J45" s="51">
+      <c r="I45" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="J45" s="23">
         <v>1</v>
       </c>
-      <c r="K45" s="51">
+      <c r="K45" s="23">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L45" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="M45" s="53">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="N45" s="53">
+      <c r="L45" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="26">
+        <v>0.35</v>
+      </c>
+      <c r="N45" s="26">
         <f t="shared" si="1"/>
-        <v>5.75</v>
-      </c>
-      <c r="O45" s="54"/>
+        <v>1.75</v>
+      </c>
+      <c r="O45" s="31"/>
     </row>
     <row r="46" spans="1:15" ht="15.75" thickBot="1">
       <c r="A46" s="1">
-        <v>56</v>
-      </c>
-      <c r="B46" s="117" t="s">
-        <v>304</v>
-      </c>
-      <c r="C46" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="116"/>
+      <c r="C46" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="E46" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="E46" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="22" t="s">
+      <c r="G46" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="G46" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="H46" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>111</v>
+      <c r="H46" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="J46" s="23">
         <v>1</v>
@@ -4319,43 +4284,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L46" s="83" t="s">
-        <v>24</v>
-      </c>
-      <c r="M46" s="64">
-        <v>0.47</v>
-      </c>
-      <c r="N46" s="37">
+      <c r="L46" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="26">
+        <v>0.96</v>
+      </c>
+      <c r="N46" s="26">
         <f t="shared" si="1"/>
-        <v>2.3499999999999996</v>
-      </c>
-      <c r="O46" s="84"/>
+        <v>4.8</v>
+      </c>
+      <c r="O46" s="32"/>
     </row>
     <row r="47" spans="1:15" ht="15.75" thickBot="1">
       <c r="A47" s="1">
-        <v>58</v>
-      </c>
-      <c r="B47" s="115"/>
+        <v>45</v>
+      </c>
+      <c r="B47" s="116"/>
       <c r="C47" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>249</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="G47" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="E47" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>253</v>
-      </c>
       <c r="I47" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J47" s="23">
         <v>1</v>
@@ -4364,43 +4329,43 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L47" s="28" t="s">
-        <v>24</v>
+      <c r="L47" s="24" t="s">
+        <v>23</v>
       </c>
       <c r="M47" s="26">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="N47" s="26">
         <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-      <c r="O47" s="31"/>
+        <v>0.75</v>
+      </c>
+      <c r="O47" s="32"/>
     </row>
     <row r="48" spans="1:15" ht="15.75" thickBot="1">
       <c r="A48" s="1">
-        <v>59</v>
-      </c>
-      <c r="B48" s="115"/>
+        <v>46</v>
+      </c>
+      <c r="B48" s="116"/>
       <c r="C48" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="G48" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="H48" s="23" t="s">
         <v>255</v>
       </c>
-      <c r="E48" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="G48" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="H48" s="21" t="s">
-        <v>22</v>
-      </c>
       <c r="I48" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J48" s="23">
         <v>1</v>
@@ -4410,42 +4375,42 @@
         <v>5</v>
       </c>
       <c r="L48" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M48" s="26">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="N48" s="26">
         <f t="shared" si="1"/>
-        <v>4.8</v>
-      </c>
-      <c r="O48" s="32"/>
+        <v>2.25</v>
+      </c>
+      <c r="O48" s="31"/>
     </row>
     <row r="49" spans="1:15" ht="15.75" thickBot="1">
       <c r="A49" s="1">
-        <v>60</v>
-      </c>
-      <c r="B49" s="115"/>
+        <v>47</v>
+      </c>
+      <c r="B49" s="116"/>
       <c r="C49" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="22" t="s">
         <v>258</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="G49" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="E49" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>261</v>
+      <c r="H49" s="23">
+        <v>1715260000</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J49" s="23">
         <v>1</v>
@@ -4455,556 +4420,510 @@
         <v>5</v>
       </c>
       <c r="L49" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M49" s="26">
-        <v>0.15</v>
+        <v>2.13</v>
       </c>
       <c r="N49" s="26">
         <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-      <c r="O49" s="32"/>
+        <v>10.649999999999999</v>
+      </c>
+      <c r="O49" s="31"/>
     </row>
     <row r="50" spans="1:15" ht="15.75" thickBot="1">
       <c r="A50" s="1">
-        <v>61</v>
-      </c>
-      <c r="B50" s="115"/>
+        <v>48</v>
+      </c>
+      <c r="B50" s="116"/>
       <c r="C50" s="20" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>266</v>
+        <v>259</v>
+      </c>
+      <c r="H50" s="23">
+        <v>1711725</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J50" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" s="23">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L50" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M50" s="26">
-        <v>0.45</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="N50" s="26">
         <f t="shared" si="1"/>
-        <v>2.25</v>
+        <v>21.12</v>
       </c>
       <c r="O50" s="31"/>
     </row>
     <row r="51" spans="1:15" ht="15.75" thickBot="1">
       <c r="A51" s="1">
-        <v>62</v>
-      </c>
-      <c r="B51" s="115"/>
-      <c r="C51" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>19</v>
+        <v>49</v>
+      </c>
+      <c r="B51" s="116"/>
+      <c r="C51" s="78" t="s">
+        <v>262</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>18</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="H51" s="23">
-        <v>1715260000</v>
-      </c>
-      <c r="I51" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="J51" s="23">
+        <v>264</v>
+      </c>
+      <c r="G51" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="J51" s="79">
         <v>1</v>
       </c>
-      <c r="K51" s="23">
+      <c r="K51" s="79">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L51" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M51" s="26">
-        <v>2.13</v>
-      </c>
-      <c r="N51" s="26">
-        <f t="shared" si="1"/>
-        <v>10.649999999999999</v>
+      <c r="L51" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="M51" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="N51" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="O51" s="31"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" thickBot="1">
       <c r="A52" s="1">
-        <v>63</v>
-      </c>
-      <c r="B52" s="115"/>
-      <c r="C52" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="116"/>
+      <c r="C52" s="78" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="D52" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="G52" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="H52" s="23">
-        <v>1711725</v>
-      </c>
-      <c r="I52" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="J52" s="23">
-        <v>2</v>
-      </c>
-      <c r="K52" s="23">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L52" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="M52" s="26">
-        <v>2.1120000000000001</v>
-      </c>
-      <c r="N52" s="26">
-        <f t="shared" si="1"/>
-        <v>21.12</v>
+      <c r="G52" s="79" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I52" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="J52" s="79">
+        <v>6</v>
+      </c>
+      <c r="K52" s="79">
+        <f t="shared" ref="K52:K59" si="2">J52*5</f>
+        <v>30</v>
+      </c>
+      <c r="L52" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="M52" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="N52" s="22" t="s">
+        <v>110</v>
       </c>
       <c r="O52" s="31"/>
     </row>
     <row r="53" spans="1:15" ht="15.75" thickBot="1">
       <c r="A53" s="1">
-        <v>64</v>
-      </c>
-      <c r="B53" s="115"/>
-      <c r="C53" s="85" t="s">
-        <v>273</v>
+        <v>51</v>
+      </c>
+      <c r="B53" s="116"/>
+      <c r="C53" s="78" t="s">
+        <v>268</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="G53" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="H53" s="22" t="s">
-        <v>22</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="G53" s="79" t="s">
+        <v>271</v>
+      </c>
+      <c r="H53" s="80"/>
       <c r="I53" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="J53" s="86">
+        <v>110</v>
+      </c>
+      <c r="J53" s="79">
         <v>1</v>
       </c>
-      <c r="K53" s="86">
-        <f t="shared" si="0"/>
+      <c r="K53" s="79">
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="L53" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M53" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N53" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O53" s="31"/>
     </row>
     <row r="54" spans="1:15" ht="15.75" thickBot="1">
       <c r="A54" s="1">
-        <v>65</v>
-      </c>
-      <c r="B54" s="115"/>
-      <c r="C54" s="85" t="s">
-        <v>276</v>
+        <v>52</v>
+      </c>
+      <c r="B54" s="117"/>
+      <c r="C54" s="81" t="s">
+        <v>272</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="G54" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="H54" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I54" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="J54" s="86">
-        <v>6</v>
-      </c>
-      <c r="K54" s="86">
-        <f t="shared" ref="K54:K61" si="2">J54*5</f>
-        <v>30</v>
-      </c>
-      <c r="L54" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="M54" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="N54" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="O54" s="31"/>
+        <v>299</v>
+      </c>
+      <c r="E54" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="74" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54" s="82" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="I54" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="J54" s="82">
+        <v>9</v>
+      </c>
+      <c r="K54" s="82">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="L54" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="M54" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="N54" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="O54" s="83"/>
     </row>
     <row r="55" spans="1:15" ht="15.75" thickBot="1">
       <c r="A55" s="1">
-        <v>66</v>
-      </c>
-      <c r="B55" s="115"/>
-      <c r="C55" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="D55" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="G55" s="86" t="s">
-        <v>282</v>
-      </c>
-      <c r="H55" s="87"/>
-      <c r="I55" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="J55" s="86">
+        <v>53</v>
+      </c>
+      <c r="B55" s="119" t="s">
+        <v>274</v>
+      </c>
+      <c r="C55" s="84" t="s">
+        <v>275</v>
+      </c>
+      <c r="D55" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E55" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="66" t="s">
+        <v>276</v>
+      </c>
+      <c r="G55" s="66" t="s">
+        <v>277</v>
+      </c>
+      <c r="H55" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="I55" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J55" s="66">
         <v>1</v>
       </c>
-      <c r="K55" s="86">
+      <c r="K55" s="66">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L55" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="M55" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="N55" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="O55" s="31"/>
+      <c r="L55" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="M55" s="86">
+        <v>14</v>
+      </c>
+      <c r="N55" s="68">
+        <f>M55*K55</f>
+        <v>70</v>
+      </c>
+      <c r="O55" s="87"/>
     </row>
     <row r="56" spans="1:15" ht="15.75" thickBot="1">
       <c r="A56" s="1">
-        <v>67</v>
-      </c>
-      <c r="B56" s="116"/>
+        <v>54</v>
+      </c>
+      <c r="B56" s="120"/>
       <c r="C56" s="88" t="s">
-        <v>283</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>284</v>
-      </c>
-      <c r="E56" s="81" t="s">
-        <v>19</v>
-      </c>
-      <c r="F56" s="81" t="s">
-        <v>285</v>
+        <v>279</v>
+      </c>
+      <c r="D56" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="89" t="s">
+        <v>280</v>
       </c>
       <c r="G56" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="H56" s="81" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="J56" s="89">
-        <v>9</v>
-      </c>
-      <c r="K56" s="89">
+        <v>281</v>
+      </c>
+      <c r="H56" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="I56" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J56" s="96">
+        <v>3</v>
+      </c>
+      <c r="K56" s="66">
         <f t="shared" si="2"/>
-        <v>45</v>
-      </c>
-      <c r="L56" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="M56" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="N56" s="81" t="s">
-        <v>111</v>
-      </c>
-      <c r="O56" s="90"/>
+        <v>15</v>
+      </c>
+      <c r="L56" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="M56" s="90">
+        <v>3.35</v>
+      </c>
+      <c r="N56" s="68">
+        <f t="shared" ref="N56:N59" si="3">M56*K56</f>
+        <v>50.25</v>
+      </c>
+      <c r="O56" s="100"/>
     </row>
     <row r="57" spans="1:15" ht="15.75" thickBot="1">
       <c r="A57" s="1">
-        <v>68</v>
-      </c>
-      <c r="B57" s="118" t="s">
-        <v>286</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B57" s="120"/>
       <c r="C57" s="91" t="s">
-        <v>287</v>
-      </c>
-      <c r="D57" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E57" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="73" t="s">
-        <v>288</v>
-      </c>
-      <c r="G57" s="73" t="s">
-        <v>289</v>
-      </c>
-      <c r="H57" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="I57" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="J57" s="73">
+        <v>282</v>
+      </c>
+      <c r="D57" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E57" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="89" t="s">
+        <v>283</v>
+      </c>
+      <c r="G57" s="66" t="s">
+        <v>284</v>
+      </c>
+      <c r="H57" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="I57" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J57" s="96">
         <v>1</v>
       </c>
-      <c r="K57" s="73">
+      <c r="K57" s="66">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L57" s="92" t="s">
-        <v>290</v>
-      </c>
-      <c r="M57" s="93">
-        <v>14</v>
-      </c>
-      <c r="N57" s="75">
-        <f>M57*K57</f>
-        <v>70</v>
-      </c>
-      <c r="O57" s="94"/>
+      <c r="L57" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="M57" s="92">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N57" s="68">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="O57" s="100"/>
     </row>
     <row r="58" spans="1:15" ht="15.75" thickBot="1">
       <c r="A58" s="1">
-        <v>69</v>
-      </c>
-      <c r="B58" s="119"/>
-      <c r="C58" s="95" t="s">
-        <v>291</v>
-      </c>
-      <c r="D58" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F58" s="96" t="s">
-        <v>292</v>
-      </c>
-      <c r="G58" s="96" t="s">
-        <v>293</v>
-      </c>
-      <c r="H58" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="I58" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="J58" s="104">
-        <v>3</v>
-      </c>
-      <c r="K58" s="73">
+        <v>56</v>
+      </c>
+      <c r="B58" s="120"/>
+      <c r="C58" s="93" t="s">
+        <v>285</v>
+      </c>
+      <c r="D58" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="66" t="s">
+        <v>286</v>
+      </c>
+      <c r="G58" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="H58" s="64" t="s">
+        <v>297</v>
+      </c>
+      <c r="I58" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J58" s="96">
+        <v>1</v>
+      </c>
+      <c r="K58" s="66">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="L58" s="92" t="s">
-        <v>290</v>
-      </c>
-      <c r="M58" s="97">
-        <v>3.35</v>
-      </c>
-      <c r="N58" s="75">
-        <f t="shared" ref="N57:N61" si="3">M58*K58</f>
-        <v>50.25</v>
-      </c>
-      <c r="O58" s="108"/>
+        <v>5</v>
+      </c>
+      <c r="L58" s="94" t="s">
+        <v>278</v>
+      </c>
+      <c r="M58" s="90">
+        <v>4.58</v>
+      </c>
+      <c r="N58" s="68">
+        <f t="shared" si="3"/>
+        <v>22.9</v>
+      </c>
+      <c r="O58" s="101" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="59" spans="1:15" ht="15.75" thickBot="1">
       <c r="A59" s="1">
-        <v>70</v>
-      </c>
-      <c r="B59" s="119"/>
-      <c r="C59" s="98" t="s">
-        <v>294</v>
-      </c>
-      <c r="D59" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E59" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F59" s="99" t="s">
-        <v>295</v>
-      </c>
-      <c r="G59" s="73" t="s">
-        <v>296</v>
-      </c>
-      <c r="H59" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="I59" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="J59" s="104">
+        <v>57</v>
+      </c>
+      <c r="B59" s="121"/>
+      <c r="C59" s="95" t="s">
+        <v>287</v>
+      </c>
+      <c r="D59" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="66" t="s">
+        <v>288</v>
+      </c>
+      <c r="G59" s="66" t="s">
+        <v>288</v>
+      </c>
+      <c r="H59" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="I59" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="J59" s="96">
         <v>1</v>
       </c>
-      <c r="K59" s="73">
+      <c r="K59" s="66">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="L59" s="92" t="s">
-        <v>290</v>
-      </c>
-      <c r="M59" s="100">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="N59" s="75">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-      <c r="O59" s="108"/>
-    </row>
-    <row r="60" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A60" s="1">
-        <v>71</v>
-      </c>
-      <c r="B60" s="119"/>
-      <c r="C60" s="101" t="s">
-        <v>297</v>
-      </c>
-      <c r="D60" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E60" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="G60" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="H60" s="71" t="s">
-        <v>309</v>
-      </c>
-      <c r="I60" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="J60" s="104">
-        <v>1</v>
-      </c>
-      <c r="K60" s="73">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L60" s="102" t="s">
-        <v>290</v>
-      </c>
-      <c r="M60" s="97">
-        <v>4.58</v>
-      </c>
-      <c r="N60" s="75">
-        <f t="shared" si="3"/>
-        <v>22.9</v>
-      </c>
-      <c r="O60" s="122" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A61" s="1">
-        <v>72</v>
-      </c>
-      <c r="B61" s="120"/>
-      <c r="C61" s="103" t="s">
-        <v>299</v>
-      </c>
-      <c r="D61" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="E61" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="F61" s="73" t="s">
-        <v>300</v>
-      </c>
-      <c r="G61" s="73" t="s">
-        <v>300</v>
-      </c>
-      <c r="H61" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="I61" s="71" t="s">
-        <v>96</v>
-      </c>
-      <c r="J61" s="104">
-        <v>1</v>
-      </c>
-      <c r="K61" s="73">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="L61" s="102" t="s">
-        <v>300</v>
-      </c>
-      <c r="M61" s="105">
+      <c r="L59" s="94" t="s">
+        <v>288</v>
+      </c>
+      <c r="M59" s="97">
         <v>3.95</v>
       </c>
-      <c r="N61" s="75">
+      <c r="N59" s="68">
         <f t="shared" si="3"/>
         <v>19.75</v>
       </c>
-      <c r="O61" s="108"/>
-    </row>
-    <row r="62" spans="1:15" ht="19.5" thickBot="1">
+      <c r="O59" s="100"/>
+    </row>
+    <row r="60" spans="1:15" ht="19.5" thickBot="1">
+      <c r="A60" s="6"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="113" t="s">
+        <v>289</v>
+      </c>
+      <c r="J60" s="113"/>
+      <c r="K60" s="113"/>
+      <c r="L60" s="113"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="9">
+        <f>SUM(N3:N59)</f>
+        <v>388.7645</v>
+      </c>
+      <c r="O60" s="7"/>
+    </row>
+    <row r="61" spans="1:15" ht="18.75">
+      <c r="A61" s="6"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="114" t="s">
+        <v>290</v>
+      </c>
+      <c r="J61" s="114"/>
+      <c r="K61" s="114"/>
+      <c r="L61" s="114"/>
+      <c r="M61" s="7"/>
+      <c r="N61" s="10">
+        <f>N60/5</f>
+        <v>77.752899999999997</v>
+      </c>
+      <c r="O61" s="7"/>
+    </row>
+    <row r="62" spans="1:15" ht="18.75">
       <c r="A62" s="6"/>
       <c r="B62" s="7"/>
       <c r="C62" s="8"/>
@@ -5013,20 +4932,19 @@
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="7"/>
-      <c r="I62" s="112" t="s">
-        <v>301</v>
-      </c>
-      <c r="J62" s="112"/>
-      <c r="K62" s="112"/>
-      <c r="L62" s="112"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="9">
-        <f>SUM(N3:N61)</f>
-        <v>389.52449999999999</v>
+      <c r="I62" s="114" t="s">
+        <v>291</v>
+      </c>
+      <c r="J62" s="114"/>
+      <c r="K62" s="114"/>
+      <c r="L62" s="114"/>
+      <c r="M62" s="7"/>
+      <c r="N62" s="26">
+        <v>88</v>
       </c>
       <c r="O62" s="7"/>
     </row>
-    <row r="63" spans="1:15" ht="18.75">
+    <row r="63" spans="1:15">
       <c r="A63" s="6"/>
       <c r="B63" s="7"/>
       <c r="C63" s="8"/>
@@ -5035,70 +4953,27 @@
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="7"/>
-      <c r="I63" s="113" t="s">
-        <v>302</v>
-      </c>
-      <c r="J63" s="113"/>
-      <c r="K63" s="113"/>
-      <c r="L63" s="113"/>
-      <c r="M63" s="7"/>
-      <c r="N63" s="10">
-        <f>N62/5</f>
-        <v>77.904899999999998</v>
-      </c>
+      <c r="I63" s="11"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="12"/>
       <c r="O63" s="7"/>
-    </row>
-    <row r="64" spans="1:15" ht="18.75">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="113" t="s">
-        <v>303</v>
-      </c>
-      <c r="J64" s="113"/>
-      <c r="K64" s="113"/>
-      <c r="L64" s="113"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="26">
-        <v>88</v>
-      </c>
-      <c r="O64" s="7"/>
-    </row>
-    <row r="65" spans="1:15">
-      <c r="A65" s="6"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="7"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="7"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="12"/>
-      <c r="O65" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="I60:L60"/>
+    <mergeCell ref="I61:L61"/>
     <mergeCell ref="I62:L62"/>
-    <mergeCell ref="I63:L63"/>
-    <mergeCell ref="I64:L64"/>
     <mergeCell ref="B3:B16"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="B20:B22"/>
     <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B27:B39"/>
-    <mergeCell ref="B40:B45"/>
-    <mergeCell ref="B46:B56"/>
-    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="B27:B37"/>
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="B44:B54"/>
+    <mergeCell ref="B55:B59"/>
   </mergeCells>
   <conditionalFormatting sqref="J7">
     <cfRule type="colorScale" priority="30">
@@ -5136,7 +5011,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N63">
+  <conditionalFormatting sqref="N61">
     <cfRule type="dataBar" priority="29">
       <dataBar>
         <cfvo type="min"/>
@@ -5174,7 +5049,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J57:J61">
+  <conditionalFormatting sqref="J55:J59">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -5196,7 +5071,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N57:N61">
+  <conditionalFormatting sqref="N55:N59">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -5232,7 +5107,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J23:J25 J56 J49 J53:J54 J39">
+  <conditionalFormatting sqref="J23:J25 J54 J47 J51:J52 J37">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -5244,7 +5119,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J23:J29 J56 J49 J39:J41 J53:J54">
+  <conditionalFormatting sqref="J23:J29 J54 J47 J37:J39 J51:J52">
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
@@ -5256,7 +5131,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J40 J26">
+  <conditionalFormatting sqref="J38 J26">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -5268,7 +5143,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41">
+  <conditionalFormatting sqref="J39">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -5280,7 +5155,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J50:J51 J34:J37 J55 J48">
+  <conditionalFormatting sqref="J48:J49 J34:J35 J53 J46">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -5302,7 +5177,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J52 J38">
+  <conditionalFormatting sqref="J50 J36">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -5324,7 +5199,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M62">
+  <conditionalFormatting sqref="M60">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -5338,7 +5213,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N64">
+  <conditionalFormatting sqref="N62">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -5420,7 +5295,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J42:J47 J30:J33">
+  <conditionalFormatting sqref="J40:J45 J30:J33">
     <cfRule type="colorScale" priority="241">
       <colorScale>
         <cfvo type="min"/>
@@ -5442,8 +5317,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N52">
-    <cfRule type="dataBar" priority="247">
+  <conditionalFormatting sqref="N3:N50">
+    <cfRule type="dataBar" priority="274">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -5456,8 +5331,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:K3 K18:K61 J4:J6 K4:K16">
-    <cfRule type="colorScale" priority="249">
+  <conditionalFormatting sqref="J3:K3 K18:K59 J4:J6 K4:K16">
+    <cfRule type="colorScale" priority="276">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5468,8 +5343,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:K16 K18:K61">
-    <cfRule type="colorScale" priority="254">
+  <conditionalFormatting sqref="K3:K16 K18:K59">
+    <cfRule type="colorScale" priority="281">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5504,37 +5379,35 @@
     <hyperlink ref="L33" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
     <hyperlink ref="L34" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
     <hyperlink ref="L35" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="L38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="L39" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="L42" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="L45" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="L48" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="L36" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="L37" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="L40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="L43" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="L46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
     <hyperlink ref="L27" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
     <hyperlink ref="L19" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
     <hyperlink ref="L20" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
     <hyperlink ref="L21" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
     <hyperlink ref="L26" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="L40" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="L38" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
     <hyperlink ref="L4" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
     <hyperlink ref="L25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="L41" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="L43" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="L44" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="L47" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="L50" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="L51" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="L52" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L49" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="L39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="L41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="L42" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="L45" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="L48" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="L49" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="L50" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="L47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
     <hyperlink ref="L17" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="L36" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="L37" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="L46" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="L61" r:id="rId49" location="technical-details" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="L22" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="L23" r:id="rId51" display="Digikey" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="L44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="L59" r:id="rId47" location="technical-details" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="L22" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="L23" r:id="rId49" display="Digikey" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId52"/>
+  <pageSetup orientation="portrait" r:id="rId50"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5549,7 +5422,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N63</xm:sqref>
+          <xm:sqref>N61</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C4DCDE22-C4C3-4E18-86E0-AE0957909D63}">
@@ -5562,7 +5435,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N57:N61</xm:sqref>
+          <xm:sqref>N55:N59</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{64D35CED-CB77-4E7D-8609-DD7C9579E340}">
@@ -5575,7 +5448,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M62</xm:sqref>
+          <xm:sqref>M60</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{603E608C-8C58-42D3-9EDD-50BEF2094DB9}">
@@ -5588,7 +5461,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N64</xm:sqref>
+          <xm:sqref>N62</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{29C5D989-E8D6-4FA3-89BC-72179293C40F}">
@@ -5601,7 +5474,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N52</xm:sqref>
+          <xm:sqref>N3:N50</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverable/Main_Board/BOM/(5 Board)Digikey_Main_Board-BOM.xlsx
+++ b/Deliverable/Main_Board/BOM/(5 Board)Digikey_Main_Board-BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GrantKros-CoopMonitor\Deliverable\Main_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FD4D53-1B78-4B70-A079-1142B38CF74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="302">
   <si>
     <t>S. No.</t>
   </si>
@@ -587,9 +586,6 @@
     <t>RES SMD 0 OHM JUMPER 1/16W 0402</t>
   </si>
   <si>
-    <t>R18, R19, RF22, RF23</t>
-  </si>
-  <si>
     <t>RC0402JR-070RL</t>
   </si>
   <si>
@@ -945,12 +941,38 @@
   </si>
   <si>
     <t>Bill of Material (BOM) for Grant Main Board</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, R19, RF22, RF23</t>
+    </r>
+  </si>
+  <si>
+    <t>Donot mount R18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="5">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
@@ -2210,7 +2232,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O63"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2227,12 +2249,12 @@
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
       <c r="A1" s="110" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B1" s="111"/>
       <c r="C1" s="111"/>
@@ -2397,7 +2419,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="98" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>31</v>
@@ -3031,7 +3053,7 @@
         <v>112</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E19" s="55" t="s">
         <v>113</v>
@@ -3240,7 +3262,7 @@
         <v>5</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M23" s="46">
         <v>1.5</v>
@@ -3491,7 +3513,7 @@
         <v>164</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E29" s="21" t="s">
         <v>153</v>
@@ -3671,41 +3693,43 @@
         <v>182</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>183</v>
+        <v>300</v>
       </c>
       <c r="E33" s="21" t="s">
         <v>153</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G33" s="23" t="s">
         <v>94</v>
       </c>
       <c r="H33" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="I33" s="21" t="s">
-        <v>186</v>
-      </c>
       <c r="J33" s="23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="23">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L33" s="24" t="s">
         <v>23</v>
       </c>
       <c r="M33" s="26">
-        <v>1.2999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="N33" s="26">
         <f t="shared" si="1"/>
-        <v>0.26</v>
-      </c>
-      <c r="O33" s="31"/>
+        <v>0.18</v>
+      </c>
+      <c r="O33" s="31" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="34" spans="1:15" ht="15.75" thickBot="1">
       <c r="A34" s="1">
@@ -3713,16 +3737,16 @@
       </c>
       <c r="B34" s="116"/>
       <c r="C34" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" s="21" t="s">
         <v>187</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>188</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>153</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G34" s="23" t="s">
         <v>94</v>
@@ -3731,7 +3755,7 @@
         <v>21</v>
       </c>
       <c r="I34" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J34" s="23">
         <v>3</v>
@@ -3758,25 +3782,25 @@
       </c>
       <c r="B35" s="116"/>
       <c r="C35" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E35" s="21" t="s">
         <v>153</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G35" s="23" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" s="21" t="s">
         <v>193</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>194</v>
       </c>
       <c r="J35" s="23">
         <v>1</v>
@@ -3803,16 +3827,16 @@
       </c>
       <c r="B36" s="116"/>
       <c r="C36" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>195</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>196</v>
       </c>
       <c r="E36" s="21" t="s">
         <v>153</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="23" t="s">
         <v>94</v>
@@ -3821,7 +3845,7 @@
         <v>21</v>
       </c>
       <c r="I36" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J36" s="23">
         <v>1</v>
@@ -3848,16 +3872,16 @@
       </c>
       <c r="B37" s="116"/>
       <c r="C37" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>199</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>200</v>
       </c>
       <c r="E37" s="21" t="s">
         <v>153</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G37" s="23" t="s">
         <v>94</v>
@@ -3866,7 +3890,7 @@
         <v>21</v>
       </c>
       <c r="I37" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J37" s="23">
         <v>1</v>
@@ -3892,22 +3916,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="115" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="D38" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="E38" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="F38" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="G38" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="G38" s="15" t="s">
-        <v>208</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>21</v>
@@ -3940,19 +3964,19 @@
       </c>
       <c r="B39" s="116"/>
       <c r="C39" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="E39" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="F39" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="G39" s="23" t="s">
         <v>213</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>214</v>
       </c>
       <c r="H39" s="21" t="s">
         <v>21</v>
@@ -3985,19 +4009,19 @@
       </c>
       <c r="B40" s="116"/>
       <c r="C40" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="E40" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="F40" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="G40" s="23" t="s">
         <v>218</v>
-      </c>
-      <c r="G40" s="23" t="s">
-        <v>219</v>
       </c>
       <c r="H40" s="21" t="s">
         <v>21</v>
@@ -4030,19 +4054,19 @@
       </c>
       <c r="B41" s="116"/>
       <c r="C41" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="E41" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="F41" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="F41" s="21" t="s">
-        <v>223</v>
-      </c>
       <c r="G41" s="23" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>21</v>
@@ -4075,19 +4099,19 @@
       </c>
       <c r="B42" s="116"/>
       <c r="C42" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="D42" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="E42" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="F42" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="E42" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>226</v>
-      </c>
       <c r="G42" s="23" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>21</v>
@@ -4120,22 +4144,22 @@
       </c>
       <c r="B43" s="117"/>
       <c r="C43" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="D43" s="49" t="s">
         <v>227</v>
       </c>
-      <c r="D43" s="49" t="s">
+      <c r="E43" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="E43" s="49" t="s">
+      <c r="F43" s="74" t="s">
         <v>229</v>
       </c>
-      <c r="F43" s="74" t="s">
+      <c r="G43" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="G43" s="50" t="s">
+      <c r="H43" s="50" t="s">
         <v>231</v>
-      </c>
-      <c r="H43" s="50" t="s">
-        <v>232</v>
       </c>
       <c r="I43" s="49" t="s">
         <v>110</v>
@@ -4164,25 +4188,25 @@
         <v>42</v>
       </c>
       <c r="B44" s="118" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C44" s="75" t="s">
+        <v>232</v>
+      </c>
+      <c r="D44" s="21" t="s">
         <v>233</v>
-      </c>
-      <c r="D44" s="21" t="s">
-        <v>234</v>
       </c>
       <c r="E44" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="G44" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="G44" s="21" t="s">
+      <c r="H44" s="23" t="s">
         <v>236</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>237</v>
       </c>
       <c r="I44" s="14" t="s">
         <v>110</v>
@@ -4212,22 +4236,22 @@
       </c>
       <c r="B45" s="116"/>
       <c r="C45" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>238</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>239</v>
       </c>
       <c r="E45" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="G45" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="H45" s="23" t="s">
         <v>241</v>
-      </c>
-      <c r="H45" s="23" t="s">
-        <v>242</v>
       </c>
       <c r="I45" s="21" t="s">
         <v>110</v>
@@ -4257,19 +4281,19 @@
       </c>
       <c r="B46" s="116"/>
       <c r="C46" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>243</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>244</v>
       </c>
       <c r="E46" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G46" s="23" t="s">
         <v>245</v>
-      </c>
-      <c r="G46" s="23" t="s">
-        <v>246</v>
       </c>
       <c r="H46" s="21" t="s">
         <v>21</v>
@@ -4302,22 +4326,22 @@
       </c>
       <c r="B47" s="116"/>
       <c r="C47" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" s="21" t="s">
         <v>247</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>248</v>
       </c>
       <c r="E47" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G47" s="23" t="s">
         <v>18</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I47" s="21" t="s">
         <v>110</v>
@@ -4347,22 +4371,22 @@
       </c>
       <c r="B48" s="116"/>
       <c r="C48" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="D48" s="21" t="s">
         <v>251</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>252</v>
       </c>
       <c r="E48" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="G48" s="23" t="s">
         <v>253</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="H48" s="23" t="s">
         <v>254</v>
-      </c>
-      <c r="H48" s="23" t="s">
-        <v>255</v>
       </c>
       <c r="I48" s="21" t="s">
         <v>110</v>
@@ -4392,19 +4416,19 @@
       </c>
       <c r="B49" s="116"/>
       <c r="C49" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="D49" s="21" t="s">
         <v>256</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>257</v>
       </c>
       <c r="E49" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="G49" s="23" t="s">
         <v>258</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>259</v>
       </c>
       <c r="H49" s="23">
         <v>1715260000</v>
@@ -4437,19 +4461,19 @@
       </c>
       <c r="B50" s="116"/>
       <c r="C50" s="20" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E50" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H50" s="23">
         <v>1711725</v>
@@ -4482,16 +4506,16 @@
       </c>
       <c r="B51" s="116"/>
       <c r="C51" s="78" t="s">
+        <v>261</v>
+      </c>
+      <c r="D51" s="22" t="s">
         <v>262</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>263</v>
       </c>
       <c r="E51" s="22" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G51" s="79" t="s">
         <v>18</v>
@@ -4526,16 +4550,16 @@
       </c>
       <c r="B52" s="116"/>
       <c r="C52" s="78" t="s">
+        <v>264</v>
+      </c>
+      <c r="D52" s="22" t="s">
         <v>265</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>266</v>
       </c>
       <c r="E52" s="22" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G52" s="79" t="s">
         <v>18</v>
@@ -4570,19 +4594,19 @@
       </c>
       <c r="B53" s="116"/>
       <c r="C53" s="78" t="s">
+        <v>267</v>
+      </c>
+      <c r="D53" s="22" t="s">
         <v>268</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>269</v>
       </c>
       <c r="E53" s="22" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="G53" s="79" t="s">
         <v>270</v>
-      </c>
-      <c r="G53" s="79" t="s">
-        <v>271</v>
       </c>
       <c r="H53" s="80"/>
       <c r="I53" s="22" t="s">
@@ -4612,16 +4636,16 @@
       </c>
       <c r="B54" s="117"/>
       <c r="C54" s="81" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E54" s="74" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="74" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G54" s="82" t="s">
         <v>18</v>
@@ -4655,10 +4679,10 @@
         <v>53</v>
       </c>
       <c r="B55" s="119" t="s">
+        <v>273</v>
+      </c>
+      <c r="C55" s="84" t="s">
         <v>274</v>
-      </c>
-      <c r="C55" s="84" t="s">
-        <v>275</v>
       </c>
       <c r="D55" s="64" t="s">
         <v>95</v>
@@ -4667,10 +4691,10 @@
         <v>18</v>
       </c>
       <c r="F55" s="66" t="s">
+        <v>275</v>
+      </c>
+      <c r="G55" s="66" t="s">
         <v>276</v>
-      </c>
-      <c r="G55" s="66" t="s">
-        <v>277</v>
       </c>
       <c r="H55" s="64" t="s">
         <v>95</v>
@@ -4686,7 +4710,7 @@
         <v>5</v>
       </c>
       <c r="L55" s="85" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M55" s="86">
         <v>14</v>
@@ -4703,7 +4727,7 @@
       </c>
       <c r="B56" s="120"/>
       <c r="C56" s="88" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D56" s="64" t="s">
         <v>95</v>
@@ -4712,10 +4736,10 @@
         <v>18</v>
       </c>
       <c r="F56" s="89" t="s">
+        <v>279</v>
+      </c>
+      <c r="G56" s="89" t="s">
         <v>280</v>
-      </c>
-      <c r="G56" s="89" t="s">
-        <v>281</v>
       </c>
       <c r="H56" s="64" t="s">
         <v>95</v>
@@ -4731,7 +4755,7 @@
         <v>15</v>
       </c>
       <c r="L56" s="85" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M56" s="90">
         <v>3.35</v>
@@ -4748,7 +4772,7 @@
       </c>
       <c r="B57" s="120"/>
       <c r="C57" s="91" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D57" s="64" t="s">
         <v>95</v>
@@ -4757,10 +4781,10 @@
         <v>18</v>
       </c>
       <c r="F57" s="89" t="s">
+        <v>282</v>
+      </c>
+      <c r="G57" s="66" t="s">
         <v>283</v>
-      </c>
-      <c r="G57" s="66" t="s">
-        <v>284</v>
       </c>
       <c r="H57" s="64" t="s">
         <v>95</v>
@@ -4776,7 +4800,7 @@
         <v>5</v>
       </c>
       <c r="L57" s="85" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M57" s="92">
         <v>9.8000000000000007</v>
@@ -4793,7 +4817,7 @@
       </c>
       <c r="B58" s="120"/>
       <c r="C58" s="93" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D58" s="64" t="s">
         <v>95</v>
@@ -4802,13 +4826,13 @@
         <v>18</v>
       </c>
       <c r="F58" s="66" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G58" s="64" t="s">
         <v>95</v>
       </c>
       <c r="H58" s="64" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I58" s="64" t="s">
         <v>95</v>
@@ -4821,7 +4845,7 @@
         <v>5</v>
       </c>
       <c r="L58" s="94" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M58" s="90">
         <v>4.58</v>
@@ -4831,7 +4855,7 @@
         <v>22.9</v>
       </c>
       <c r="O58" s="101" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="15.75" thickBot="1">
@@ -4840,7 +4864,7 @@
       </c>
       <c r="B59" s="121"/>
       <c r="C59" s="95" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D59" s="64" t="s">
         <v>95</v>
@@ -4849,10 +4873,10 @@
         <v>18</v>
       </c>
       <c r="F59" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G59" s="66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H59" s="64" t="s">
         <v>95</v>
@@ -4868,7 +4892,7 @@
         <v>5</v>
       </c>
       <c r="L59" s="94" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M59" s="97">
         <v>3.95</v>
@@ -4889,7 +4913,7 @@
       <c r="G60" s="6"/>
       <c r="H60" s="7"/>
       <c r="I60" s="113" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J60" s="113"/>
       <c r="K60" s="113"/>
@@ -4897,7 +4921,7 @@
       <c r="M60" s="10"/>
       <c r="N60" s="9">
         <f>SUM(N3:N59)</f>
-        <v>388.7645</v>
+        <v>388.68449999999996</v>
       </c>
       <c r="O60" s="7"/>
     </row>
@@ -4911,7 +4935,7 @@
       <c r="G61" s="6"/>
       <c r="H61" s="7"/>
       <c r="I61" s="114" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J61" s="114"/>
       <c r="K61" s="114"/>
@@ -4919,7 +4943,7 @@
       <c r="M61" s="7"/>
       <c r="N61" s="10">
         <f>N60/5</f>
-        <v>77.752899999999997</v>
+        <v>77.736899999999991</v>
       </c>
       <c r="O61" s="7"/>
     </row>
@@ -4933,7 +4957,7 @@
       <c r="G62" s="6"/>
       <c r="H62" s="7"/>
       <c r="I62" s="114" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J62" s="114"/>
       <c r="K62" s="114"/>
@@ -5356,55 +5380,55 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="L6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="L8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="L9" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="L10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="L11" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="L12" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="L13" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="L14" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="L15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="L16" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="L18" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="L24" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="L28" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="L29" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="L30" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="L31" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="L32" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="L33" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="L34" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="L35" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="L36" r:id="rId24" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="L37" r:id="rId25" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="L40" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="L43" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="L46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="L27" r:id="rId29" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="L19" r:id="rId30" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="L20" r:id="rId31" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="L21" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="L26" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="L38" r:id="rId34" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="L4" r:id="rId35" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="L25" r:id="rId36" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="L39" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="L41" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="L42" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="L45" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="L48" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="L49" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="L50" r:id="rId43" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="L47" r:id="rId44" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="L17" r:id="rId45" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="L44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="L59" r:id="rId47" location="technical-details" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="L22" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="L23" r:id="rId49" display="Digikey" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="L3" r:id="rId1"/>
+    <hyperlink ref="L5" r:id="rId2"/>
+    <hyperlink ref="L6" r:id="rId3"/>
+    <hyperlink ref="L7" r:id="rId4"/>
+    <hyperlink ref="L8" r:id="rId5"/>
+    <hyperlink ref="L9" r:id="rId6"/>
+    <hyperlink ref="L10" r:id="rId7"/>
+    <hyperlink ref="L11" r:id="rId8"/>
+    <hyperlink ref="L12" r:id="rId9"/>
+    <hyperlink ref="L13" r:id="rId10"/>
+    <hyperlink ref="L14" r:id="rId11"/>
+    <hyperlink ref="L15" r:id="rId12"/>
+    <hyperlink ref="L16" r:id="rId13"/>
+    <hyperlink ref="L18" r:id="rId14"/>
+    <hyperlink ref="L24" r:id="rId15"/>
+    <hyperlink ref="L28" r:id="rId16"/>
+    <hyperlink ref="L29" r:id="rId17"/>
+    <hyperlink ref="L30" r:id="rId18"/>
+    <hyperlink ref="L31" r:id="rId19"/>
+    <hyperlink ref="L32" r:id="rId20"/>
+    <hyperlink ref="L33" r:id="rId21"/>
+    <hyperlink ref="L34" r:id="rId22"/>
+    <hyperlink ref="L35" r:id="rId23"/>
+    <hyperlink ref="L36" r:id="rId24"/>
+    <hyperlink ref="L37" r:id="rId25"/>
+    <hyperlink ref="L40" r:id="rId26"/>
+    <hyperlink ref="L43" r:id="rId27"/>
+    <hyperlink ref="L46" r:id="rId28"/>
+    <hyperlink ref="L27" r:id="rId29"/>
+    <hyperlink ref="L19" r:id="rId30"/>
+    <hyperlink ref="L20" r:id="rId31"/>
+    <hyperlink ref="L21" r:id="rId32"/>
+    <hyperlink ref="L26" r:id="rId33"/>
+    <hyperlink ref="L38" r:id="rId34"/>
+    <hyperlink ref="L4" r:id="rId35"/>
+    <hyperlink ref="L25" r:id="rId36"/>
+    <hyperlink ref="L39" r:id="rId37"/>
+    <hyperlink ref="L41" r:id="rId38"/>
+    <hyperlink ref="L42" r:id="rId39"/>
+    <hyperlink ref="L45" r:id="rId40"/>
+    <hyperlink ref="L48" r:id="rId41"/>
+    <hyperlink ref="L49" r:id="rId42"/>
+    <hyperlink ref="L50" r:id="rId43"/>
+    <hyperlink ref="L47" r:id="rId44"/>
+    <hyperlink ref="L17" r:id="rId45"/>
+    <hyperlink ref="L44" r:id="rId46"/>
+    <hyperlink ref="L59" r:id="rId47" location="technical-details"/>
+    <hyperlink ref="L22" r:id="rId48"/>
+    <hyperlink ref="L23" r:id="rId49" display="Digikey"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId50"/>
